--- a/unit-0/paneltalk-agenda/agenda.xlsx
+++ b/unit-0/paneltalk-agenda/agenda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Documents/git/Hdip2025/workshop-1-3/unit-0/paneltalk-agenda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{59332476-843A-BF4F-8913-EC96DB36E001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE46EC25-F92B-3742-B777-AC283309599A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="20920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -138,6 +138,9 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">Industry Engagement - </t>
+    </r>
+    <r>
       <rPr>
         <i/>
         <sz val="11"/>
@@ -145,7 +148,43 @@
         <rFont val="Helvetica Neue"/>
         <family val="2"/>
       </rPr>
-      <t>Web Dev Lab/overview - John and Pete (Room TBD)</t>
+      <t>Joan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="12"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Auditorium)</t>
+    </r>
+  </si>
+  <si>
+    <t>Technical Interviews, CVs, Career Planning - John Rellis and Joan (Auditorium)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Devops - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFEFEFE"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>Richard</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FFFEFEFE"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> and Jimmy (F02)</t>
     </r>
     <r>
       <rPr>
@@ -160,16 +199,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Devops - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFEFEFE"/>
-        <rFont val="Helvetica Neue"/>
-        <family val="2"/>
-      </rPr>
-      <t>Richard</t>
+      <t xml:space="preserve">Full Stack I - </t>
     </r>
     <r>
       <rPr>
@@ -179,7 +209,50 @@
         <rFont val="Helvetica Neue"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> and Jimmy (Room TBD)</t>
+      <t>Eamonn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="12"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Full Stack II - </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FFFEFEFE"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>Frank</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="12"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+ (F02)
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FFFEFEFE"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>Web Dev Lab/overview - John and Pete (Auditorium)</t>
     </r>
     <r>
       <rPr>
@@ -194,7 +267,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Industry Engagement - </t>
+      <t xml:space="preserve">Project Status - </t>
     </r>
     <r>
       <rPr>
@@ -204,80 +277,7 @@
         <rFont val="Helvetica Neue"/>
         <family val="2"/>
       </rPr>
-      <t>Joan</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="12"/>
-        <rFont val="Helvetica Neue"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (Auditorium)</t>
-    </r>
-  </si>
-  <si>
-    <t>Technical Interviews, CVs, Career Planning - John Rellis and Joan (Auditorium)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Full Stack I - </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FFFEFEFE"/>
-        <rFont val="Helvetica Neue"/>
-        <family val="2"/>
-      </rPr>
-      <t>Eamonn</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="12"/>
-        <rFont val="Helvetica Neue"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Full Stack II - </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FFFEFEFE"/>
-        <rFont val="Helvetica Neue"/>
-        <family val="2"/>
-      </rPr>
-      <t>Frank</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="12"/>
-        <rFont val="Helvetica Neue"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
- (Room TBD)
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Project Status - </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FFFEFEFE"/>
-        <rFont val="Helvetica Neue"/>
-        <family val="2"/>
-      </rPr>
-      <t>Colm  (Room TBD)</t>
+      <t>Colm  (F02)</t>
     </r>
     <r>
       <rPr>
@@ -311,7 +311,7 @@
         <rFont val="Helvetica Neue"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">  (Room TBD)</t>
+      <t xml:space="preserve">  (F02)</t>
     </r>
   </si>
 </sst>
@@ -643,7 +643,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -695,6 +695,84 @@
     <xf numFmtId="20" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -703,87 +781,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1930,13 +1927,13 @@
   <sheetData>
     <row r="1" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="2" spans="2:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
     </row>
     <row r="3" spans="2:6" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="1"/>
@@ -1958,44 +1955,44 @@
       <c r="C4" s="5">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="19"/>
-      <c r="F4" s="36"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="17"/>
     </row>
     <row r="5" spans="2:6" ht="46" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="6"/>
       <c r="C5" s="5">
         <v>0.42708333333333331</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="19"/>
-      <c r="F5" s="37"/>
+      <c r="E5" s="45"/>
+      <c r="F5"/>
     </row>
     <row r="6" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="6"/>
       <c r="C6" s="5">
         <v>0.4375</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="19"/>
-      <c r="F6" s="37"/>
+      <c r="E6" s="45"/>
+      <c r="F6"/>
     </row>
     <row r="7" spans="2:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="7"/>
       <c r="C7" s="8">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="19"/>
-      <c r="F7" s="37"/>
+      <c r="E7" s="45"/>
+      <c r="F7"/>
     </row>
     <row r="8" spans="2:6" ht="60" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="9"/>
@@ -2006,9 +2003,9 @@
         <v>15</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="41" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2017,22 +2014,22 @@
       <c r="C9" s="5">
         <v>0.5</v>
       </c>
-      <c r="D9" s="27" t="s">
-        <v>16</v>
+      <c r="D9" s="23" t="s">
+        <v>20</v>
       </c>
       <c r="E9" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="39"/>
+        <v>19</v>
+      </c>
+      <c r="F9" s="42"/>
     </row>
     <row r="10" spans="2:6" ht="50" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="6"/>
       <c r="C10" s="5">
         <v>0.52083333333333337</v>
       </c>
-      <c r="D10" s="45"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="44" t="s">
+      <c r="D10" s="24"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="18" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2041,22 +2038,22 @@
       <c r="C11" s="8">
         <v>0.54166666666666663</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
     </row>
     <row r="12" spans="2:6" ht="41" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="6"/>
       <c r="C12" s="5">
         <v>0.57291666666666663</v>
       </c>
-      <c r="D12" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="29"/>
-      <c r="F12" s="32" t="s">
+      <c r="D12" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="31"/>
+      <c r="F12" s="34" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2065,44 +2062,44 @@
       <c r="C13" s="5">
         <v>44839.59375</v>
       </c>
-      <c r="D13" s="30"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="26"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="35"/>
     </row>
     <row r="14" spans="2:6" ht="43" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="12"/>
       <c r="C14" s="8">
         <v>44839.614583333336</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
     </row>
     <row r="15" spans="2:6" ht="89" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="6"/>
       <c r="C15" s="5">
         <v>44839.635416666664</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="D15" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="42" t="s">
-        <v>19</v>
-      </c>
-      <c r="F15" s="43"/>
+      <c r="E15" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="40"/>
     </row>
     <row r="16" spans="2:6" ht="25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="6"/>
       <c r="C16" s="16">
         <v>0.67708333333333337</v>
       </c>
-      <c r="D16" s="33"/>
-      <c r="E16" s="40" t="s">
+      <c r="D16" s="36"/>
+      <c r="E16" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="41"/>
+      <c r="F16" s="20"/>
     </row>
     <row r="17" spans="2:6" ht="55" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="6"/>
@@ -2112,22 +2109,27 @@
       <c r="D17" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="34"/>
-      <c r="F17" s="35"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="22"/>
     </row>
     <row r="18" spans="2:6" ht="38" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="12"/>
       <c r="C18" s="13">
         <v>44839.708333333336</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="D18" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="E18" s="23"/>
-      <c r="F18" s="24"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D4:E4"/>
     <mergeCell ref="E16:F17"/>
     <mergeCell ref="D9:D10"/>
     <mergeCell ref="E9:E10"/>
@@ -2139,11 +2141,6 @@
     <mergeCell ref="D14:F14"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="F8:F9"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D4:E4"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup scale="70" orientation="portrait"/>

--- a/unit-0/paneltalk-agenda/agenda.xlsx
+++ b/unit-0/paneltalk-agenda/agenda.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Documents/git/Hdip2025/workshop-1-3/unit-0/paneltalk-agenda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE46EC25-F92B-3742-B777-AC283309599A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{222ABF27-1C60-1A4C-BE6A-153494C8EC13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="20920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3440" yWindow="1060" windowWidth="31940" windowHeight="20420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1-1 - Workshop 1, 3 &amp; 5 -" sheetId="3" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Time</t>
   </si>
@@ -32,9 +32,6 @@
   </si>
   <si>
     <t>Coffee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Workshop 1, 3 &amp; 5 -January 10 </t>
   </si>
   <si>
     <t>2025 Class</t>
@@ -52,59 +49,43 @@
     <t>GrowthHub</t>
   </si>
   <si>
-    <t>To Be discussed with Margaret Tynan</t>
-  </si>
-  <si>
     <t xml:space="preserve">Programming Lab - Siobhan, Mairead and Pete </t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Registration </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FFFEFEFE"/>
-        <rFont val="Helvetica Neue"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Auditorium)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="12"/>
-        <rFont val="Helvetica Neue"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">Welcome, Agenda and Introductions (Auditorium)
 </t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Online Learning Experience - </t>
+    <t>Technical Interviews, CVs, Career Planning - John Rellis and Joan (Auditorium)</t>
+  </si>
+  <si>
+    <t>Higher Diploma in Computer Science</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Workshop 1, 3 &amp; 5 -January 10th 2025</t>
+  </si>
+  <si>
+    <t>More Information to follow</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Registration </t>
     </r>
     <r>
       <rPr>
         <i/>
-        <sz val="11"/>
+        <sz val="14"/>
         <color rgb="FFFEFEFE"/>
-        <rFont val="Helvetica Neue"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>Laura (Auditorium)</t>
+      <t>(Auditorium)</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="14"/>
         <color indexed="12"/>
-        <rFont val="Helvetica Neue"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">
@@ -113,23 +94,23 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Programme Overview - </t>
+      <t xml:space="preserve">Online Learning Experience - </t>
     </r>
     <r>
       <rPr>
         <i/>
-        <sz val="11"/>
+        <sz val="14"/>
         <color rgb="FFFEFEFE"/>
-        <rFont val="Helvetica Neue"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>Eamonn and Frank (Auditorium)</t>
+      <t>Laura (Auditorium)</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="14"/>
         <color indexed="12"/>
-        <rFont val="Helvetica Neue"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">
@@ -138,59 +119,23 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Industry Engagement - </t>
+      <t xml:space="preserve">Programme Overview - </t>
     </r>
     <r>
       <rPr>
         <i/>
-        <sz val="11"/>
+        <sz val="14"/>
         <color rgb="FFFEFEFE"/>
-        <rFont val="Helvetica Neue"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>Joan</t>
+      <t>Eamonn and Frank (Auditorium)</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="14"/>
         <color indexed="12"/>
-        <rFont val="Helvetica Neue"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (Auditorium)</t>
-    </r>
-  </si>
-  <si>
-    <t>Technical Interviews, CVs, Career Planning - John Rellis and Joan (Auditorium)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Devops - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFEFEFE"/>
-        <rFont val="Helvetica Neue"/>
-        <family val="2"/>
-      </rPr>
-      <t>Richard</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FFFEFEFE"/>
-        <rFont val="Helvetica Neue"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> and Jimmy (F02)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="12"/>
-        <rFont val="Helvetica Neue"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">
@@ -199,23 +144,179 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Full Stack I - </t>
+      <t xml:space="preserve">Devops - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFEFEFE"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Richard</t>
     </r>
     <r>
       <rPr>
         <i/>
-        <sz val="11"/>
+        <sz val="14"/>
         <color rgb="FFFEFEFE"/>
-        <rFont val="Helvetica Neue"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>Eamonn</t>
+      <t xml:space="preserve"> and Jimmy (F02)</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="14"/>
         <color indexed="12"/>
-        <rFont val="Helvetica Neue"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color rgb="FFFEFEFE"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Web Dev Lab/overview - John and Pete (Auditorium)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color indexed="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Industry Engagement - </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color rgb="FFFEFEFE"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Joan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color indexed="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Auditorium)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Project Status - </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color rgb="FFFEFEFE"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Colm  (F02)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color indexed="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Consulation Sessions (Optional) - </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color rgb="FFFEFEFE"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hdip Team</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color indexed="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  (F02)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Online Learning Experience -                 </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color rgb="FFFEFEFE"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Laura (Auditorium)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color indexed="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">
+Full Stack I - </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color rgb="FFFEFEFE"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Eamonn
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color indexed="12"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">
@@ -224,94 +325,23 @@
     <r>
       <rPr>
         <i/>
-        <sz val="11"/>
+        <sz val="14"/>
         <color rgb="FFFEFEFE"/>
-        <rFont val="Helvetica Neue"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
       <t>Frank</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="14"/>
         <color indexed="12"/>
-        <rFont val="Helvetica Neue"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">
  (F02)
 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FFFEFEFE"/>
-        <rFont val="Helvetica Neue"/>
-        <family val="2"/>
-      </rPr>
-      <t>Web Dev Lab/overview - John and Pete (Auditorium)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="12"/>
-        <rFont val="Helvetica Neue"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Project Status - </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FFFEFEFE"/>
-        <rFont val="Helvetica Neue"/>
-        <family val="2"/>
-      </rPr>
-      <t>Colm  (F02)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="12"/>
-        <rFont val="Helvetica Neue"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Consulation Sessions (Optional) - </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FFFEFEFE"/>
-        <rFont val="Helvetica Neue"/>
-        <family val="2"/>
-      </rPr>
-      <t>Hdip Team</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="12"/>
-        <rFont val="Helvetica Neue"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  (F02)</t>
     </r>
   </si>
 </sst>
@@ -326,67 +356,69 @@
       <name val="Helvetica Neue"/>
     </font>
     <font>
+      <b/>
+      <sz val="20"/>
+      <color indexed="8"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <sz val="12"/>
       <color indexed="12"/>
-      <name val="Helvetica Neue"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="10"/>
+      <sz val="12"/>
       <color indexed="12"/>
-      <name val="Helvetica Neue"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color indexed="12"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
+      <sz val="14"/>
+      <color indexed="12"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color indexed="12"/>
-      <name val="Helvetica Neue"/>
+      <sz val="14"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="13"/>
-      <color indexed="12"/>
-      <name val="Helvetica Neue"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="13"/>
-      <color indexed="12"/>
-      <name val="Helvetica Neue"/>
+      <sz val="14"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="11"/>
+      <sz val="14"/>
       <color rgb="FFFEFEFE"/>
-      <name val="Helvetica Neue"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="14"/>
       <color rgb="FFFEFEFE"/>
-      <name val="Helvetica Neue"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -405,31 +437,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="15"/>
-        <bgColor auto="1"/>
+        <fgColor rgb="FFFF7942"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="16"/>
-        <bgColor auto="1"/>
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="17"/>
-        <bgColor auto="1"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="18"/>
-        <bgColor auto="1"/>
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAB7942"/>
+        <fgColor theme="9" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -643,144 +675,159 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -856,7 +903,16 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
     <mruColors>
-      <color rgb="FFAB7942"/>
+      <color rgb="FFFF2600"/>
+      <color rgb="FF942092"/>
+      <color rgb="FFFF7942"/>
+      <color rgb="FFB8AAEA"/>
+      <color rgb="FFFFC7A0"/>
+      <color rgb="FF00CDBE"/>
+      <color rgb="FF00FDFF"/>
+      <color rgb="FF73FDD6"/>
+      <color rgb="FFFF7E79"/>
+      <color rgb="FF9437FF"/>
     </mruColors>
   </colors>
   <extLst>
@@ -868,6 +924,759 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>685800</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>444500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{780F4798-C2F6-181E-D058-BAB8FB4DE3F5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4699000" y="165100"/>
+          <a:ext cx="457200" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>787400</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1244600</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>444500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CF8BBBF-AFA5-37D9-376E-4E6C45CFA56F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5257800" y="165100"/>
+          <a:ext cx="457200" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1320800</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1778000</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>431800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C57A3E31-D4E8-7269-5861-E6AF173E22F6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5791200" y="152400"/>
+          <a:ext cx="457200" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1828800</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2286000</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F30B39A-DE2A-5448-9267-2432DAA17E63}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6604000" y="1003300"/>
+          <a:ext cx="457200" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2349500</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2806700</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74907396-A984-B742-9387-FF0742BE9D22}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7124700" y="990600"/>
+          <a:ext cx="457200" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2590800</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3048000</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>647700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB8CF7E7-75F7-5348-AB7D-4049840031B7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10007600" y="2959100"/>
+          <a:ext cx="457200" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2628900</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3086100</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7C265E0-4DD0-AA4E-9002-09670200CE68}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10045700" y="5803900"/>
+          <a:ext cx="457200" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2654300</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3111500</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>469900</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85A4C45A-A33B-4F4C-877D-9B73D4C4526B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10071100" y="7188200"/>
+          <a:ext cx="457200" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2679700</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3136900</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>215900</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC0FC077-A711-0647-B0D6-F8DB01EA1D5F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10096500" y="8382000"/>
+          <a:ext cx="457200" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2425700</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>558800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2882900</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>254000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B67DAEB8-C697-6A47-9A74-1B27256680A0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6896100" y="3327400"/>
+          <a:ext cx="457200" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2374900</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2832100</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C55C8EC5-098B-2F4B-B7D9-AC4BEA834E36}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6845300" y="5689600"/>
+          <a:ext cx="457200" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2146300</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2603500</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>469900</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Picture 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DF46787-CA56-F64D-96A4-FAC0129FF44E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9563100" y="7188200"/>
+          <a:ext cx="457200" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2146300</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2603500</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>215900</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Picture 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67072245-D456-554A-8D9E-13C29873FF6C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9563100" y="8382000"/>
+          <a:ext cx="457200" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2552700</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>546100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>3009900</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>241300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Picture 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F089C03E-1346-444E-B22B-CA7E03C5F918}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4254500" y="3314700"/>
+          <a:ext cx="457200" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1841500</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2298700</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>508000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Picture 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A6499E9-A399-6E43-AEE9-7DFAD2572BB1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6311900" y="5676900"/>
+          <a:ext cx="457200" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2578100</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>3035300</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>520700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="Picture 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B315C7DE-BE47-FB40-A084-87432CB3EEEF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4279900" y="7239000"/>
+          <a:ext cx="457200" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2565400</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>3022600</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>508000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="Picture 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED633031-4CBF-D249-93FE-27D26338A17C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4267200" y="8674100"/>
+          <a:ext cx="457200" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1915,221 +2724,219 @@
   <dimension ref="B1:F18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="4.83203125" style="14" customWidth="1"/>
-    <col min="2" max="2" width="6.1640625" style="14" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" style="14" customWidth="1"/>
-    <col min="4" max="4" width="36.33203125" style="14" customWidth="1"/>
-    <col min="5" max="5" width="38.6640625" style="14" customWidth="1"/>
-    <col min="6" max="6" width="42.5" style="14" customWidth="1"/>
-    <col min="7" max="7" width="16.33203125" style="14" customWidth="1"/>
-    <col min="8" max="16384" width="16.33203125" style="14"/>
+    <col min="1" max="1" width="4.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6.1640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="40.33203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="38.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="42.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.33203125" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="16.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="2" spans="2:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B2" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
+    <row r="1" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="2"/>
+    </row>
+    <row r="2" spans="2:6" ht="43" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="F2" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="3" spans="2:6" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B3" s="1"/>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="10"/>
+      <c r="C3" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="12" t="s">
         <v>6</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B4" s="4"/>
-      <c r="C4" s="5">
+      <c r="B4" s="13"/>
+      <c r="C4" s="14">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D4" s="44" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="45"/>
+      <c r="D4" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="16"/>
       <c r="F4" s="17"/>
     </row>
     <row r="5" spans="2:6" ht="46" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B5" s="6"/>
-      <c r="C5" s="5">
+      <c r="B5" s="18"/>
+      <c r="C5" s="14">
         <v>0.42708333333333331</v>
       </c>
-      <c r="D5" s="44" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="45"/>
-      <c r="F5"/>
+      <c r="D5" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="16"/>
+      <c r="F5" s="19"/>
     </row>
     <row r="6" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="6"/>
-      <c r="C6" s="5">
+      <c r="B6" s="18"/>
+      <c r="C6" s="14">
         <v>0.4375</v>
       </c>
-      <c r="D6" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="45"/>
-      <c r="F6"/>
+      <c r="D6" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="16"/>
+      <c r="F6" s="19"/>
     </row>
     <row r="7" spans="2:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="7"/>
-      <c r="C7" s="8">
+      <c r="B7" s="20"/>
+      <c r="C7" s="21">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D7" s="37" t="s">
+      <c r="D7" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="45"/>
-      <c r="F7"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="19"/>
     </row>
     <row r="8" spans="2:6" ht="60" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B8" s="9"/>
-      <c r="C8" s="5">
+      <c r="B8" s="24"/>
+      <c r="C8" s="14">
         <v>0.47916666666666669</v>
       </c>
-      <c r="D8" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="11" t="s">
+      <c r="D8" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="41" t="s">
-        <v>9</v>
+      <c r="F8" s="27" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="60" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="6"/>
-      <c r="C9" s="5">
+      <c r="B9" s="18"/>
+      <c r="C9" s="14">
         <v>0.5</v>
       </c>
-      <c r="D9" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="25" t="s">
+      <c r="D9" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="42"/>
+      <c r="E9" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="30"/>
     </row>
     <row r="10" spans="2:6" ht="50" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="6"/>
-      <c r="C10" s="5">
+      <c r="B10" s="18"/>
+      <c r="C10" s="14">
         <v>0.52083333333333337</v>
       </c>
-      <c r="D10" s="24"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="18" t="s">
-        <v>10</v>
+      <c r="D10" s="31"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="33" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="55" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="7"/>
-      <c r="C11" s="8">
+      <c r="B11" s="20"/>
+      <c r="C11" s="21">
         <v>0.54166666666666663</v>
       </c>
-      <c r="D11" s="37" t="s">
+      <c r="D11" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
     </row>
     <row r="12" spans="2:6" ht="41" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="6"/>
-      <c r="C12" s="5">
+      <c r="B12" s="18"/>
+      <c r="C12" s="14">
         <v>0.57291666666666663</v>
       </c>
-      <c r="D12" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" s="31"/>
-      <c r="F12" s="34" t="s">
+      <c r="D12" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="36"/>
+      <c r="F12" s="37" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="38" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B13" s="6"/>
-      <c r="C13" s="5">
+      <c r="B13" s="18"/>
+      <c r="C13" s="14">
         <v>44839.59375</v>
       </c>
-      <c r="D13" s="32"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="35"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="40"/>
     </row>
     <row r="14" spans="2:6" ht="43" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B14" s="12"/>
-      <c r="C14" s="8">
+      <c r="B14" s="41"/>
+      <c r="C14" s="21">
         <v>44839.614583333336</v>
       </c>
-      <c r="D14" s="37" t="s">
+      <c r="D14" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
     </row>
     <row r="15" spans="2:6" ht="89" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B15" s="6"/>
-      <c r="C15" s="5">
+      <c r="B15" s="18"/>
+      <c r="C15" s="14">
         <v>44839.635416666664</v>
       </c>
-      <c r="D15" s="23" t="s">
+      <c r="D15" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="F15" s="40"/>
+      <c r="F15" s="43"/>
     </row>
     <row r="16" spans="2:6" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="6"/>
-      <c r="C16" s="16">
+      <c r="B16" s="18"/>
+      <c r="C16" s="44">
         <v>0.67708333333333337</v>
       </c>
-      <c r="D16" s="36"/>
-      <c r="E16" s="19" t="s">
+      <c r="D16" s="45"/>
+      <c r="E16" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="20"/>
+      <c r="F16" s="47"/>
     </row>
     <row r="17" spans="2:6" ht="55" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="6"/>
-      <c r="C17" s="16">
+      <c r="B17" s="18"/>
+      <c r="C17" s="44">
         <v>0.6875</v>
       </c>
-      <c r="D17" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="21"/>
-      <c r="F17" s="22"/>
+      <c r="D17" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="49"/>
+      <c r="F17" s="50"/>
     </row>
     <row r="18" spans="2:6" ht="38" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="12"/>
-      <c r="C18" s="13">
+      <c r="B18" s="6"/>
+      <c r="C18" s="5">
         <v>44839.708333333336</v>
       </c>
-      <c r="D18" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="28"/>
-      <c r="F18" s="29"/>
+      <c r="D18" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="8"/>
+      <c r="F18" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D4:E4"/>
     <mergeCell ref="E16:F17"/>
     <mergeCell ref="D9:D10"/>
     <mergeCell ref="E9:E10"/>
@@ -2141,11 +2948,17 @@
     <mergeCell ref="D14:F14"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="F8:F9"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="C1:D2"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup scale="70" orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;11&amp;K000000&amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/unit-0/paneltalk-agenda/agenda.xlsx
+++ b/unit-0/paneltalk-agenda/agenda.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Documents/git/Hdip2025/workshop-1-3/unit-0/paneltalk-agenda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{222ABF27-1C60-1A4C-BE6A-153494C8EC13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DA2633E-C591-E147-9BC2-BEB91BCFD090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3440" yWindow="1060" windowWidth="31940" windowHeight="20420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2760" yWindow="500" windowWidth="33760" windowHeight="20980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1-1 - Workshop 1, 3 &amp; 5 -" sheetId="3" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Time</t>
   </si>
@@ -46,9 +46,6 @@
     <t>Workshop Close_x000B_</t>
   </si>
   <si>
-    <t>GrowthHub</t>
-  </si>
-  <si>
     <t xml:space="preserve">Programming Lab - Siobhan, Mairead and Pete </t>
   </si>
   <si>
@@ -65,9 +62,6 @@
     <t xml:space="preserve"> Workshop 1, 3 &amp; 5 -January 10th 2025</t>
   </si>
   <si>
-    <t>More Information to follow</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Registration </t>
     </r>
@@ -105,31 +99,6 @@
         <family val="2"/>
       </rPr>
       <t>Laura (Auditorium)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color indexed="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Programme Overview - </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="14"/>
-        <color rgb="FFFEFEFE"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Eamonn and Frank (Auditorium)</t>
     </r>
     <r>
       <rPr>
@@ -343,6 +312,41 @@
  (F02)
 </t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Programme Overview - </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color rgb="FFFEFEFE"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Frank (Auditorium)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color indexed="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t>The path to completion 
+GrowthHub</t>
+  </si>
+  <si>
+    <t>Dr Margaret Tynan</t>
+  </si>
+  <si>
+    <t>Registration (Auditorium)</t>
   </si>
 </sst>
 </file>
@@ -682,12 +686,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -697,15 +695,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -721,112 +710,127 @@
     <xf numFmtId="20" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2721,7 +2725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B1:F18"/>
+  <dimension ref="B1:G18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="1" customWidth="1"/>
@@ -2729,214 +2733,223 @@
     <col min="3" max="3" width="11.33203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="40.33203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="38.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="42.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="42.1640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.33203125" style="1" hidden="1" customWidth="1"/>
     <col min="8" max="16384" width="16.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C1" s="2" t="s">
+    <row r="1" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C1" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="49"/>
+    </row>
+    <row r="2" spans="2:7" ht="43" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="F2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="2"/>
     </row>
-    <row r="2" spans="2:6" ht="43" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="F2" s="4" t="s">
+    <row r="3" spans="2:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B3" s="5"/>
+      <c r="C3" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B4" s="8"/>
+      <c r="C4" s="9">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D4" s="46" t="s">
         <v>13</v>
       </c>
+      <c r="E4" s="47"/>
+      <c r="F4" s="10"/>
     </row>
-    <row r="3" spans="2:6" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B3" s="10"/>
-      <c r="C3" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>6</v>
-      </c>
+    <row r="5" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B5" s="11"/>
+      <c r="C5" s="9">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D5" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="47"/>
+      <c r="F5" s="12"/>
     </row>
-    <row r="4" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B4" s="13"/>
-      <c r="C4" s="14">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D4" s="15" t="s">
+    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B6" s="11"/>
+      <c r="C6" s="9">
+        <v>0.4375</v>
+      </c>
+      <c r="D6" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="47"/>
+      <c r="F6" s="12"/>
+    </row>
+    <row r="7" spans="2:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B7" s="13"/>
+      <c r="C7" s="14">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D7" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="48"/>
+      <c r="F7" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="48"/>
+    </row>
+    <row r="8" spans="2:7" ht="60" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B8" s="15"/>
+      <c r="C8" s="9">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="16"/>
-      <c r="F4" s="17"/>
+      <c r="F8" s="44" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="5" spans="2:6" ht="46" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B5" s="18"/>
-      <c r="C5" s="14">
-        <v>0.42708333333333331</v>
-      </c>
-      <c r="D5" s="15" t="s">
+    <row r="9" spans="2:7" ht="60" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B9" s="11"/>
+      <c r="C9" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="45"/>
+    </row>
+    <row r="10" spans="2:7" ht="50" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B10" s="11"/>
+      <c r="C10" s="9">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D10" s="27"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" ht="55" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B11" s="13"/>
+      <c r="C11" s="14">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D11" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+    </row>
+    <row r="12" spans="2:7" ht="41" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B12" s="11"/>
+      <c r="C12" s="9">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="D12" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="34"/>
+      <c r="F12" s="37" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="38" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B13" s="11"/>
+      <c r="C13" s="9">
+        <v>44839.59375</v>
+      </c>
+      <c r="D13" s="35"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="38"/>
+    </row>
+    <row r="14" spans="2:7" ht="43" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B14" s="20"/>
+      <c r="C14" s="14">
+        <v>44839.614583333336</v>
+      </c>
+      <c r="D14" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+    </row>
+    <row r="15" spans="2:7" ht="89" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B15" s="11"/>
+      <c r="C15" s="9">
+        <v>44839.635416666664</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="42" t="s">
         <v>10</v>
-      </c>
-      <c r="E5" s="16"/>
-      <c r="F5" s="19"/>
-    </row>
-    <row r="6" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="18"/>
-      <c r="C6" s="14">
-        <v>0.4375</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="16"/>
-      <c r="F6" s="19"/>
-    </row>
-    <row r="7" spans="2:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="20"/>
-      <c r="C7" s="21">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="23"/>
-      <c r="F7" s="19"/>
-    </row>
-    <row r="8" spans="2:6" ht="60" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B8" s="24"/>
-      <c r="C8" s="14">
-        <v>0.47916666666666669</v>
-      </c>
-      <c r="D8" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="27" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" ht="60" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="18"/>
-      <c r="C9" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" s="30"/>
-    </row>
-    <row r="10" spans="2:6" ht="50" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="18"/>
-      <c r="C10" s="14">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D10" s="31"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="33" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" ht="55" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="20"/>
-      <c r="C11" s="21">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="D11" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-    </row>
-    <row r="12" spans="2:6" ht="41" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="18"/>
-      <c r="C12" s="14">
-        <v>0.57291666666666663</v>
-      </c>
-      <c r="D12" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="36"/>
-      <c r="F12" s="37" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6" ht="38" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B13" s="18"/>
-      <c r="C13" s="14">
-        <v>44839.59375</v>
-      </c>
-      <c r="D13" s="38"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="40"/>
-    </row>
-    <row r="14" spans="2:6" ht="43" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B14" s="41"/>
-      <c r="C14" s="21">
-        <v>44839.614583333336</v>
-      </c>
-      <c r="D14" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
-    </row>
-    <row r="15" spans="2:6" ht="89" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B15" s="18"/>
-      <c r="C15" s="14">
-        <v>44839.635416666664</v>
-      </c>
-      <c r="D15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="42" t="s">
-        <v>11</v>
       </c>
       <c r="F15" s="43"/>
     </row>
-    <row r="16" spans="2:6" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="18"/>
-      <c r="C16" s="44">
+    <row r="16" spans="2:7" ht="25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B16" s="11"/>
+      <c r="C16" s="21">
         <v>0.67708333333333337</v>
       </c>
-      <c r="D16" s="45"/>
-      <c r="E16" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16" s="47"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="23"/>
     </row>
     <row r="17" spans="2:6" ht="55" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="18"/>
-      <c r="C17" s="44">
+      <c r="B17" s="11"/>
+      <c r="C17" s="21">
         <v>0.6875</v>
       </c>
-      <c r="D17" s="48" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="49"/>
-      <c r="F17" s="50"/>
+      <c r="D17" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="24"/>
+      <c r="F17" s="25"/>
     </row>
     <row r="18" spans="2:6" ht="38" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="6"/>
-      <c r="C18" s="5">
+      <c r="B18" s="4"/>
+      <c r="C18" s="3">
         <v>44839.708333333336</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="8"/>
-      <c r="F18" s="9"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="32"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="C1:D2"/>
     <mergeCell ref="E16:F17"/>
     <mergeCell ref="D9:D10"/>
     <mergeCell ref="E9:E10"/>
@@ -2948,11 +2961,6 @@
     <mergeCell ref="D14:F14"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="F8:F9"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="C1:D2"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup scale="70" orientation="portrait"/>

--- a/unit-0/paneltalk-agenda/agenda.xlsx
+++ b/unit-0/paneltalk-agenda/agenda.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Documents/git/Hdip2025/workshop-1-3/unit-0/paneltalk-agenda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DA2633E-C591-E147-9BC2-BEB91BCFD090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13DE25C2-BAB1-E54F-B4FD-38201A4A68F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="500" windowWidth="33760" windowHeight="20980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1-1 - Workshop 1, 3 &amp; 5 -" sheetId="3" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Time</t>
   </si>
@@ -46,9 +46,6 @@
     <t>Workshop Close_x000B_</t>
   </si>
   <si>
-    <t xml:space="preserve">Programming Lab - Siobhan, Mairead and Pete </t>
-  </si>
-  <si>
     <t xml:space="preserve">Welcome, Agenda and Introductions (Auditorium)
 </t>
   </si>
@@ -147,6 +144,9 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">Industry Engagement - </t>
+    </r>
+    <r>
       <rPr>
         <i/>
         <sz val="14"/>
@@ -154,7 +154,31 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>Web Dev Lab/overview - John and Pete (Auditorium)</t>
+      <t>Joan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color indexed="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Auditorium)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Project Status - </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color rgb="FFFEFEFE"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Colm  (F02)</t>
     </r>
     <r>
       <rPr>
@@ -169,55 +193,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Industry Engagement - </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="14"/>
-        <color rgb="FFFEFEFE"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Joan</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color indexed="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (Auditorium)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Project Status - </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="14"/>
-        <color rgb="FFFEFEFE"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Colm  (F02)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color indexed="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Consulation Sessions (Optional) - </t>
     </r>
     <r>
@@ -238,31 +213,6 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">  (F02)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Online Learning Experience -                 </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="14"/>
-        <color rgb="FFFEFEFE"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Laura (Auditorium)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color indexed="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
     </r>
   </si>
   <si>
@@ -310,31 +260,6 @@
       </rPr>
       <t xml:space="preserve">
  (F02)
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Programme Overview - </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="14"/>
-        <color rgb="FFFEFEFE"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Frank (Auditorium)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color indexed="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
 </t>
     </r>
   </si>
@@ -347,6 +272,85 @@
   </si>
   <si>
     <t>Registration (Auditorium)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color rgb="FFFEFEFE"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Web Dev Lab - John  (Auditorium)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color indexed="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Programme Overview - </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color rgb="FFFEFEFE"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Frank and Siobhan(Auditorium)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color indexed="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Slack Ovrview - Pete (Auditorium)</t>
+  </si>
+  <si>
+    <t>Programming Lab - Siobhan, Mairead and Pete 
+(IT221, IT220)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Online Learning Experience: Managing Expectations  -                                          </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color rgb="FFFEFEFE"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Laura (F03)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color indexed="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -746,6 +750,27 @@
     <xf numFmtId="20" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -759,9 +784,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -800,9 +822,6 @@
     <xf numFmtId="49" fontId="5" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -816,21 +835,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1595,15 +1599,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>2578100</xdr:colOff>
+      <xdr:colOff>2527300</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
+      <xdr:rowOff>711200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>3035300</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>520700</xdr:rowOff>
+      <xdr:colOff>2984500</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1626,7 +1630,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4279900" y="7239000"/>
+          <a:off x="4229100" y="7886700"/>
           <a:ext cx="457200" cy="457200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1639,15 +1643,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>2565400</xdr:colOff>
+      <xdr:colOff>2540000</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>50800</xdr:rowOff>
+      <xdr:rowOff>241300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>3022600</xdr:colOff>
+      <xdr:colOff>2997200</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>508000</xdr:rowOff>
+      <xdr:rowOff>698500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1670,7 +1674,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4267200" y="8674100"/>
+          <a:off x="4241800" y="8864600"/>
           <a:ext cx="457200" cy="457200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2739,16 +2743,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C1" s="49" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="49"/>
+      <c r="C1" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="27"/>
     </row>
     <row r="2" spans="2:7" ht="43" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
       <c r="F2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -2771,10 +2775,10 @@
       <c r="C4" s="9">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D4" s="46" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="47"/>
+      <c r="D4" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="26"/>
       <c r="F4" s="10"/>
     </row>
     <row r="5" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.15">
@@ -2782,10 +2786,10 @@
       <c r="C5" s="9">
         <v>0.42708333333333331</v>
       </c>
-      <c r="D5" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="47"/>
+      <c r="D5" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="26"/>
       <c r="F5" s="12"/>
     </row>
     <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
@@ -2793,10 +2797,10 @@
       <c r="C6" s="9">
         <v>0.4375</v>
       </c>
-      <c r="D6" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="47"/>
+      <c r="D6" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="26"/>
       <c r="F6" s="12"/>
     </row>
     <row r="7" spans="2:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -2804,14 +2808,14 @@
       <c r="C7" s="14">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D7" s="40" t="s">
+      <c r="D7" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="48"/>
-      <c r="F7" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" s="48"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="24"/>
     </row>
     <row r="8" spans="2:7" ht="60" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="15"/>
@@ -2819,13 +2823,13 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="44" t="s">
-        <v>23</v>
+        <v>14</v>
+      </c>
+      <c r="F8" s="49" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="2:7" ht="60" customHeight="1" x14ac:dyDescent="0.15">
@@ -2833,23 +2837,25 @@
       <c r="C9" s="9">
         <v>0.5</v>
       </c>
-      <c r="D9" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" s="45"/>
+      <c r="D9" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="50"/>
     </row>
     <row r="10" spans="2:7" ht="50" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="11"/>
       <c r="C10" s="9">
         <v>0.52083333333333337</v>
       </c>
-      <c r="D10" s="27"/>
-      <c r="E10" s="29"/>
+      <c r="D10" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="35"/>
       <c r="F10" s="19" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="55" customHeight="1" x14ac:dyDescent="0.15">
@@ -2857,23 +2863,23 @@
       <c r="C11" s="14">
         <v>0.54166666666666663</v>
       </c>
-      <c r="D11" s="40" t="s">
+      <c r="D11" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
     </row>
     <row r="12" spans="2:7" ht="41" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="11"/>
       <c r="C12" s="9">
         <v>0.57291666666666663</v>
       </c>
-      <c r="D12" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="34"/>
-      <c r="F12" s="37" t="s">
-        <v>18</v>
+      <c r="D12" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="40"/>
+      <c r="F12" s="43" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="38" customHeight="1" x14ac:dyDescent="0.15">
@@ -2881,77 +2887,71 @@
       <c r="C13" s="9">
         <v>44839.59375</v>
       </c>
-      <c r="D13" s="35"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="38"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="44"/>
     </row>
     <row r="14" spans="2:7" ht="43" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="20"/>
       <c r="C14" s="14">
         <v>44839.614583333336</v>
       </c>
-      <c r="D14" s="40" t="s">
+      <c r="D14" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
     </row>
     <row r="15" spans="2:7" ht="89" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="11"/>
       <c r="C15" s="9">
         <v>44839.635416666664</v>
       </c>
-      <c r="D15" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="43"/>
+      <c r="D15" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="48"/>
     </row>
     <row r="16" spans="2:7" ht="25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="11"/>
       <c r="C16" s="21">
         <v>0.67708333333333337</v>
       </c>
-      <c r="D16" s="39"/>
-      <c r="E16" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="23"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="30"/>
     </row>
-    <row r="17" spans="2:6" ht="55" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6" ht="75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="11"/>
       <c r="C17" s="21">
         <v>0.6875</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="24"/>
-      <c r="F17" s="25"/>
+        <v>26</v>
+      </c>
+      <c r="E17" s="31"/>
+      <c r="F17" s="32"/>
     </row>
     <row r="18" spans="2:6" ht="38" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4"/>
       <c r="C18" s="3">
         <v>44839.708333333336</v>
       </c>
-      <c r="D18" s="30" t="s">
+      <c r="D18" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="31"/>
-      <c r="F18" s="32"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="38"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D4:E4"/>
+  <mergeCells count="16">
     <mergeCell ref="C1:D2"/>
     <mergeCell ref="E16:F17"/>
-    <mergeCell ref="D9:D10"/>
     <mergeCell ref="E9:E10"/>
     <mergeCell ref="D18:F18"/>
     <mergeCell ref="D12:E13"/>
@@ -2961,6 +2961,11 @@
     <mergeCell ref="D14:F14"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="F8:F9"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D4:E4"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup scale="70" orientation="portrait"/>

--- a/unit-0/paneltalk-agenda/agenda.xlsx
+++ b/unit-0/paneltalk-agenda/agenda.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Documents/git/Hdip2025/workshop-1-3/unit-0/paneltalk-agenda/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/edeleastar/workshop-1-3/unit-0/paneltalk-agenda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13DE25C2-BAB1-E54F-B4FD-38201A4A68F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{636D3B34-44E2-CC49-BFB2-6E17425F1551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="24420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1-1 - Workshop 1, 3 &amp; 5 -" sheetId="3" r:id="rId1"/>
@@ -50,9 +50,6 @@
 </t>
   </si>
   <si>
-    <t>Technical Interviews, CVs, Career Planning - John Rellis and Joan (Auditorium)</t>
-  </si>
-  <si>
     <t>Higher Diploma in Computer Science</t>
   </si>
   <si>
@@ -351,6 +348,10 @@
       <t xml:space="preserve">
 </t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Technical Interviews, CVs, Career Planning - John Rellis  SETU, Wei Kit Wong, Kargo and Joan (Auditorium)</t>
   </si>
 </sst>
 </file>
@@ -753,7 +754,79 @@
     <xf numFmtId="49" fontId="5" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
@@ -764,78 +837,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2743,16 +2744,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C1" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="27"/>
+      <c r="C1" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="23"/>
     </row>
     <row r="2" spans="2:7" ht="43" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
       <c r="F2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -2775,10 +2776,10 @@
       <c r="C4" s="9">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D4" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="26"/>
+      <c r="D4" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="50"/>
       <c r="F4" s="10"/>
     </row>
     <row r="5" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.15">
@@ -2786,10 +2787,10 @@
       <c r="C5" s="9">
         <v>0.42708333333333331</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="26"/>
+      <c r="E5" s="50"/>
       <c r="F5" s="12"/>
     </row>
     <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
@@ -2797,10 +2798,10 @@
       <c r="C6" s="9">
         <v>0.4375</v>
       </c>
-      <c r="D6" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="26"/>
+      <c r="D6" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="50"/>
       <c r="F6" s="12"/>
     </row>
     <row r="7" spans="2:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -2808,14 +2809,14 @@
       <c r="C7" s="14">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="24"/>
-      <c r="F7" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="24"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="48"/>
     </row>
     <row r="8" spans="2:7" ht="60" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="15"/>
@@ -2823,13 +2824,13 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="49" t="s">
-        <v>19</v>
+        <v>13</v>
+      </c>
+      <c r="F8" s="46" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="2:7" ht="60" customHeight="1" x14ac:dyDescent="0.15">
@@ -2838,12 +2839,12 @@
         <v>0.5</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="50"/>
+        <v>21</v>
+      </c>
+      <c r="E9" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="47"/>
     </row>
     <row r="10" spans="2:7" ht="50" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="11"/>
@@ -2851,11 +2852,11 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="35"/>
+        <v>23</v>
+      </c>
+      <c r="E10" s="30"/>
       <c r="F10" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="55" customHeight="1" x14ac:dyDescent="0.15">
@@ -2863,23 +2864,23 @@
       <c r="C11" s="14">
         <v>0.54166666666666663</v>
       </c>
-      <c r="D11" s="23" t="s">
+      <c r="D11" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
     </row>
     <row r="12" spans="2:7" ht="41" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="11"/>
       <c r="C12" s="9">
         <v>0.57291666666666663</v>
       </c>
-      <c r="D12" s="39" t="s">
+      <c r="D12" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="35"/>
+      <c r="F12" s="38" t="s">
         <v>15</v>
-      </c>
-      <c r="E12" s="40"/>
-      <c r="F12" s="43" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="38" customHeight="1" x14ac:dyDescent="0.15">
@@ -2887,44 +2888,44 @@
       <c r="C13" s="9">
         <v>44839.59375</v>
       </c>
-      <c r="D13" s="41"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="44"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="39"/>
     </row>
     <row r="14" spans="2:7" ht="43" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="20"/>
       <c r="C14" s="14">
         <v>44839.614583333336</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="D14" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
     </row>
     <row r="15" spans="2:7" ht="89" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="11"/>
       <c r="C15" s="9">
         <v>44839.635416666664</v>
       </c>
-      <c r="D15" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="48"/>
+      <c r="D15" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="45"/>
     </row>
     <row r="16" spans="2:7" ht="25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="11"/>
       <c r="C16" s="21">
         <v>0.67708333333333337</v>
       </c>
-      <c r="D16" s="45"/>
-      <c r="E16" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="F16" s="30"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="26"/>
     </row>
     <row r="17" spans="2:6" ht="75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="11"/>
@@ -2932,21 +2933,21 @@
         <v>0.6875</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="31"/>
-      <c r="F17" s="32"/>
+        <v>25</v>
+      </c>
+      <c r="E17" s="27"/>
+      <c r="F17" s="28"/>
     </row>
     <row r="18" spans="2:6" ht="38" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4"/>
       <c r="C18" s="3">
         <v>44839.708333333336</v>
       </c>
-      <c r="D18" s="36" t="s">
+      <c r="D18" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="37"/>
-      <c r="F18" s="38"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="16">

--- a/unit-0/paneltalk-agenda/agenda.xlsx
+++ b/unit-0/paneltalk-agenda/agenda.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/edeleastar/workshop-1-3/unit-0/paneltalk-agenda/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\CertCompScience\workshop1-3\unit-0\paneltalk-agenda\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{636D3B34-44E2-CC49-BFB2-6E17425F1551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C639764B-F324-42AB-836B-045C5CEE9835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="24420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-9660" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1-1 - Workshop 1, 3 &amp; 5 -" sheetId="3" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Time</t>
   </si>
@@ -34,76 +34,10 @@
     <t>Coffee</t>
   </si>
   <si>
-    <t>2025 Class</t>
-  </si>
-  <si>
     <t>2024 Class</t>
   </si>
   <si>
-    <t>2023 Class</t>
-  </si>
-  <si>
     <t>Workshop Close_x000B_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Welcome, Agenda and Introductions (Auditorium)
-</t>
-  </si>
-  <si>
-    <t>Higher Diploma in Computer Science</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Workshop 1, 3 &amp; 5 -January 10th 2025</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Registration </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="14"/>
-        <color rgb="FFFEFEFE"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Auditorium)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color indexed="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Online Learning Experience - </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="14"/>
-        <color rgb="FFFEFEFE"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Laura (Auditorium)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color indexed="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
   </si>
   <si>
     <r>
@@ -165,55 +99,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Project Status - </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="14"/>
-        <color rgb="FFFEFEFE"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Colm  (F02)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color indexed="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Consulation Sessions (Optional) - </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="14"/>
-        <color rgb="FFFEFEFE"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Hdip Team</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color indexed="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  (F02)</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">
 Full Stack I - </t>
     </r>
@@ -271,6 +156,23 @@
     <t>Registration (Auditorium)</t>
   </si>
   <si>
+    <t>2025 Cert Class</t>
+  </si>
+  <si>
+    <t>2025 HDip Class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registration 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Welcome, Agenda and Introductions 
+</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Online Learning Experience - </t>
+    </r>
     <r>
       <rPr>
         <i/>
@@ -279,7 +181,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>Web Dev Lab - John  (Auditorium)</t>
+      <t>Laura</t>
     </r>
     <r>
       <rPr>
@@ -293,72 +195,42 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Programme Overview - </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="14"/>
-        <color rgb="FFFEFEFE"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Frank and Siobhan(Auditorium)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color indexed="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
+    <t>Some sort of meet and greet actviity</t>
   </si>
   <si>
-    <t>Slack Ovrview - Pete (Auditorium)</t>
+    <t xml:space="preserve">Computer Systems and Networks (Caroline and Frank)
+</t>
   </si>
   <si>
-    <t>Programming Lab - Siobhan, Mairead and Pete 
-(IT221, IT220)</t>
+    <t>Databases - Roseanne and Mary</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Online Learning Experience: Managing Expectations  -                                          </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="14"/>
-        <color rgb="FFFEFEFE"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Laura (F03)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color indexed="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
+    <t xml:space="preserve">Overview of Follow-on Courses
 </t>
-    </r>
+  </si>
+  <si>
+    <t>Project Status - Colm</t>
   </si>
   <si>
     <t xml:space="preserve">
-Technical Interviews, CVs, Career Planning - John Rellis  SETU, Wei Kit Wong, Kargo and Joan (Auditorium)</t>
+Interview Intelligence: Humans, AI, and the Future of Hiring - Joan (TBD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Online Learning Experience: Managing Expectations  -                                          Laura
+</t>
+  </si>
+  <si>
+    <t>Cert/Higher Diploma in Computer Science</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Workshop 1, 3 &amp; 5 -January 16th 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -431,7 +303,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -446,36 +318,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF7942"/>
+        <fgColor rgb="FF5BA4BB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="-0.249977111117893"/>
+        <fgColor rgb="FFDFDA70"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFC979B"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
+        <fgColor rgb="FFEFBC65"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="-0.499984740745262"/>
+        <fgColor rgb="FF95CA73"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -530,17 +408,6 @@
       <top style="thin">
         <color indexed="14"/>
       </top>
-      <bottom style="thin">
-        <color indexed="14"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="14"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -574,29 +441,7 @@
       <left style="thin">
         <color indexed="14"/>
       </left>
-      <right style="thin">
-        <color indexed="14"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="14"/>
-      </left>
       <right/>
-      <top style="thin">
-        <color indexed="14"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="14"/>
-      </right>
       <top style="thin">
         <color indexed="14"/>
       </top>
@@ -635,45 +480,64 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="14"/>
+      <left style="medium">
+        <color indexed="64"/>
       </left>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="14"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="14"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="14"/>
+      <top style="medium">
+        <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color indexed="14"/>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="14"/>
+      <top style="medium">
+        <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -684,7 +548,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -715,7 +579,7 @@
     <xf numFmtId="20" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -733,110 +597,113 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="20" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -912,16 +779,16 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
     <mruColors>
+      <color rgb="FF95CA73"/>
+      <color rgb="FF7275A7"/>
+      <color rgb="FFEFBC65"/>
+      <color rgb="FFFC979B"/>
+      <color rgb="FFDFDA70"/>
+      <color rgb="FF5BA4BB"/>
+      <color rgb="FF8F6B9F"/>
+      <color rgb="FFFFC7A0"/>
       <color rgb="FFFF2600"/>
       <color rgb="FF942092"/>
-      <color rgb="FFFF7942"/>
-      <color rgb="FFB8AAEA"/>
-      <color rgb="FFFFC7A0"/>
-      <color rgb="FF00CDBE"/>
-      <color rgb="FF00FDFF"/>
-      <color rgb="FF73FDD6"/>
-      <color rgb="FFFF7E79"/>
-      <color rgb="FF9437FF"/>
     </mruColors>
   </colors>
   <extLst>
@@ -940,22 +807,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
+      <xdr:colOff>145415</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>165100</xdr:rowOff>
+      <xdr:rowOff>149860</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>685800</xdr:colOff>
+      <xdr:colOff>593090</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
+      <xdr:rowOff>421640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{780F4798-C2F6-181E-D058-BAB8FB4DE3F5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CF8BBBF-AFA5-37D9-376E-4E6C45CFA56F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -971,8 +838,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4699000" y="165100"/>
-          <a:ext cx="457200" cy="457200"/>
+          <a:off x="4431665" y="149860"/>
+          <a:ext cx="457200" cy="443230"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -984,22 +851,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>787400</xdr:colOff>
+      <xdr:colOff>650240</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>165100</xdr:rowOff>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>1244600</xdr:colOff>
+      <xdr:colOff>1107440</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
+      <xdr:rowOff>435610</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
+        <xdr:cNvPr id="4" name="Picture 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CF8BBBF-AFA5-37D9-376E-4E6C45CFA56F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C57A3E31-D4E8-7269-5861-E6AF173E22F6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1015,8 +882,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5257800" y="165100"/>
-          <a:ext cx="457200" cy="457200"/>
+          <a:off x="4936490" y="142875"/>
+          <a:ext cx="457200" cy="454660"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1028,22 +895,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>1320800</xdr:colOff>
+      <xdr:colOff>1162050</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>1778000</xdr:colOff>
+      <xdr:colOff>1618884</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>431800</xdr:rowOff>
+      <xdr:rowOff>438150</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
+        <xdr:cNvPr id="19" name="Picture 18" descr="A white numbers on an orange background&#10;&#10;AI-generated content may be incorrect.">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C57A3E31-D4E8-7269-5861-E6AF173E22F6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09DB44E9-E284-BA25-92F0-AC6FD543A269}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1052,15 +919,21 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5791200" y="152400"/>
-          <a:ext cx="457200" cy="457200"/>
+          <a:off x="5448300" y="152400"/>
+          <a:ext cx="456834" cy="457200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1072,22 +945,272 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>1828800</xdr:colOff>
+      <xdr:colOff>2068830</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>2286000</xdr:colOff>
+      <xdr:colOff>2533284</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
+      <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4">
+        <xdr:cNvPr id="20" name="Picture 19" descr="A white numbers on an orange background&#10;&#10;AI-generated content may be incorrect.">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F30B39A-DE2A-5448-9267-2432DAA17E63}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE521803-46EE-4B3A-B09F-7DD55A9DFFD5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6355080" y="981075"/>
+          <a:ext cx="464454" cy="447675"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2205990</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>390525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2670444</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="Picture 20" descr="A white numbers on an orange background&#10;&#10;AI-generated content may be incorrect.">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6EC9B8DF-50DB-4E3F-829B-57CF27E70ED4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3729990" y="3895725"/>
+          <a:ext cx="464454" cy="453390"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>989330</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1463309</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="Picture 21" descr="A white numbers on an orange background&#10;&#10;AI-generated content may be incorrect.">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA83024B-AE35-4E62-B157-8C13D8CB88EC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7923530" y="5674995"/>
+          <a:ext cx="477789" cy="468630"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2196465</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>769620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2651394</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>97155</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="Picture 22" descr="A white numbers on an orange background&#10;&#10;AI-generated content may be incorrect.">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02166AB7-D031-4A3A-82B4-28AF1A9349E8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3720465" y="7894320"/>
+          <a:ext cx="460644" cy="461010"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1931670</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>453390</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2417079</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>897255</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="Picture 23" descr="A white numbers on an orange background&#10;&#10;AI-generated content may be incorrect.">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FF679BE-E969-4F5B-B678-0730DA09F110}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6217920" y="9016365"/>
+          <a:ext cx="475884" cy="443865"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1590675</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2036445</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>77470</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="26" name="Picture 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E74083B2-8C6A-4ADA-9C32-D84FC4E9E2F9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1103,8 +1226,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6604000" y="1003300"/>
-          <a:ext cx="457200" cy="457200"/>
+          <a:off x="5876925" y="962025"/>
+          <a:ext cx="457200" cy="458470"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1116,22 +1239,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>2349500</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:colOff>2158365</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>201930</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>2806700</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:colOff>2611755</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>668020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5">
+        <xdr:cNvPr id="27" name="Picture 26">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74907396-A984-B742-9387-FF0742BE9D22}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07AB22B7-FF4E-44F8-8926-E2D353770AB5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1140,15 +1263,15 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7124700" y="990600"/>
-          <a:ext cx="457200" cy="457200"/>
+          <a:off x="6444615" y="3707130"/>
+          <a:ext cx="461010" cy="462280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1160,22 +1283,110 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>2590800</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
+      <xdr:colOff>1497330</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>3048000</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>647700</xdr:rowOff>
+      <xdr:colOff>1958340</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>22225</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6">
+        <xdr:cNvPr id="28" name="Picture 27">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB8CF7E7-75F7-5348-AB7D-4049840031B7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA4F9E65-3C1C-4028-8C65-EACE4D6E70D1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8431530" y="5676900"/>
+          <a:ext cx="457200" cy="458470"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1762125</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>533400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2225040</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>437515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="29" name="Picture 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33AA9BF5-7EF8-49A2-9E4C-841C4FB49926}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8696325" y="7115175"/>
+          <a:ext cx="457200" cy="458470"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2295525</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2758440</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>439420</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="31" name="Picture 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{959AEB4B-8ACA-4E26-BC16-044174F31851}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1191,8 +1402,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10007600" y="2959100"/>
-          <a:ext cx="457200" cy="457200"/>
+          <a:off x="9229725" y="3505200"/>
+          <a:ext cx="457200" cy="439420"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1204,22 +1415,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>2628900</xdr:colOff>
+      <xdr:colOff>2005965</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>177800</xdr:rowOff>
+      <xdr:rowOff>93345</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>3086100</xdr:colOff>
+      <xdr:colOff>2459355</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>16510</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 7">
+        <xdr:cNvPr id="32" name="Picture 31">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7C265E0-4DD0-AA4E-9002-09670200CE68}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86F43DC2-0804-4D15-B675-499174D2603A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1235,8 +1446,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10045700" y="5803900"/>
-          <a:ext cx="457200" cy="457200"/>
+          <a:off x="8940165" y="5684520"/>
+          <a:ext cx="457200" cy="429895"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1248,22 +1459,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>2654300</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:colOff>2247900</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>533400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>3111500</xdr:colOff>
+      <xdr:colOff>2705100</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>469900</xdr:rowOff>
+      <xdr:rowOff>435610</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8">
+        <xdr:cNvPr id="33" name="Picture 32">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85A4C45A-A33B-4F4C-877D-9B73D4C4526B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F717819D-DC57-4FEB-BB80-97E5B5A28978}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1279,8 +1490,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10071100" y="7188200"/>
-          <a:ext cx="457200" cy="457200"/>
+          <a:off x="9182100" y="7115175"/>
+          <a:ext cx="457200" cy="439420"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1292,22 +1503,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>2679700</xdr:colOff>
+      <xdr:colOff>2331720</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>154305</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>3136900</xdr:colOff>
+      <xdr:colOff>2779395</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>215900</xdr:rowOff>
+      <xdr:rowOff>287020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 9">
+        <xdr:cNvPr id="34" name="Picture 33">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC0FC077-A711-0647-B0D6-F8DB01EA1D5F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1D55DB7-9099-4D05-A743-12105CAB99C1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1323,8 +1534,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10096500" y="8382000"/>
-          <a:ext cx="457200" cy="457200"/>
+          <a:off x="9265920" y="8402955"/>
+          <a:ext cx="447675" cy="433705"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1336,22 +1547,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>2425700</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>558800</xdr:rowOff>
+      <xdr:colOff>1348740</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>472440</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>2882900</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>254000</xdr:rowOff>
+      <xdr:colOff>1807845</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>930910</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 10">
+        <xdr:cNvPr id="35" name="Picture 34">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B67DAEB8-C697-6A47-9A74-1B27256680A0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{182A83A7-BE57-4F0B-BB97-5EC434986ADE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1367,316 +1578,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6896100" y="3327400"/>
-          <a:ext cx="457200" cy="457200"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>2374900</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>2832100</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Picture 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C55C8EC5-098B-2F4B-B7D9-AC4BEA834E36}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6845300" y="5689600"/>
-          <a:ext cx="457200" cy="457200"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>2146300</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>2603500</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>469900</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Picture 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DF46787-CA56-F64D-96A4-FAC0129FF44E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9563100" y="7188200"/>
-          <a:ext cx="457200" cy="457200"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>2146300</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>2603500</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>215900</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Picture 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67072245-D456-554A-8D9E-13C29873FF6C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9563100" y="8382000"/>
-          <a:ext cx="457200" cy="457200"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2552700</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>546100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>3009900</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>241300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="Picture 14">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F089C03E-1346-444E-B22B-CA7E03C5F918}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4254500" y="3314700"/>
-          <a:ext cx="457200" cy="457200"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1841500</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>50800</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>2298700</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>508000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="Picture 15">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A6499E9-A399-6E43-AEE9-7DFAD2572BB1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6311900" y="5676900"/>
-          <a:ext cx="457200" cy="457200"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2527300</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>711200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2984500</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="Picture 16">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B315C7DE-BE47-FB40-A084-87432CB3EEEF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4229100" y="7886700"/>
-          <a:ext cx="457200" cy="457200"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2540000</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>241300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2997200</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>698500</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="Picture 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED633031-4CBF-D249-93FE-27D26338A17C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4241800" y="8864600"/>
-          <a:ext cx="457200" cy="457200"/>
+          <a:off x="5634990" y="9035415"/>
+          <a:ext cx="459105" cy="458470"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2731,232 +2634,230 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:G18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="16.33203125" defaultRowHeight="19.95" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="4.83203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6.1640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="4.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6.109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="40.33203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="38.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="42.1640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="42.109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="16.33203125" style="1" hidden="1" customWidth="1"/>
     <col min="8" max="16384" width="16.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C1" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="23"/>
+    <row r="1" spans="2:7" ht="13.95" customHeight="1">
+      <c r="C1" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="17"/>
     </row>
-    <row r="2" spans="2:7" ht="43" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
+    <row r="2" spans="2:7" ht="43.05" customHeight="1">
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
       <c r="F2" s="2" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
-    <row r="3" spans="2:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:7" ht="19.95" customHeight="1">
       <c r="B3" s="5"/>
       <c r="C3" s="6" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>6</v>
-      </c>
     </row>
-    <row r="4" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:7" ht="30" customHeight="1">
       <c r="B4" s="8"/>
       <c r="C4" s="9">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D4" s="49" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="50"/>
+      <c r="D4" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="46"/>
       <c r="F4" s="10"/>
     </row>
-    <row r="5" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:7" ht="46.05" customHeight="1">
       <c r="B5" s="11"/>
       <c r="C5" s="9">
         <v>0.42708333333333331</v>
       </c>
-      <c r="D5" s="49" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="50"/>
+      <c r="D5" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="46"/>
       <c r="F5" s="12"/>
     </row>
-    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:7" ht="30" customHeight="1">
       <c r="B6" s="11"/>
       <c r="C6" s="9">
         <v>0.4375</v>
       </c>
-      <c r="D6" s="49" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="50"/>
+      <c r="D6" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="46"/>
       <c r="F6" s="12"/>
     </row>
-    <row r="7" spans="2:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:7" ht="35.25" customHeight="1">
       <c r="B7" s="13"/>
       <c r="C7" s="14">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D7" s="42" t="s">
+      <c r="D7" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="48"/>
-      <c r="F7" s="42" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" s="48"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="20"/>
     </row>
-    <row r="8" spans="2:7" ht="60" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:7" ht="60" customHeight="1">
       <c r="B8" s="15"/>
       <c r="C8" s="9">
         <v>0.47916666666666669</v>
       </c>
-      <c r="D8" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="46" t="s">
-        <v>18</v>
+      <c r="D8" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="9" spans="2:7" ht="60" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:7" ht="60" customHeight="1">
       <c r="B9" s="11"/>
       <c r="C9" s="9">
         <v>0.5</v>
       </c>
-      <c r="D9" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="47"/>
+      <c r="D9" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="39"/>
     </row>
-    <row r="10" spans="2:7" ht="50" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:7" ht="49.95" customHeight="1">
       <c r="B10" s="11"/>
       <c r="C10" s="9">
         <v>0.52083333333333337</v>
       </c>
-      <c r="D10" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="30"/>
-      <c r="F10" s="19" t="s">
+      <c r="D10" s="30" t="s">
         <v>19</v>
       </c>
+      <c r="E10" s="37"/>
+      <c r="F10" s="40" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="11" spans="2:7" ht="55" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:7" ht="55.05" customHeight="1">
       <c r="B11" s="13"/>
       <c r="C11" s="14">
         <v>0.54166666666666663</v>
       </c>
-      <c r="D11" s="42" t="s">
+      <c r="D11" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
     </row>
-    <row r="12" spans="2:7" ht="41" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:7" ht="40.950000000000003" customHeight="1">
       <c r="B12" s="11"/>
       <c r="C12" s="9">
         <v>0.57291666666666663</v>
       </c>
-      <c r="D12" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="35"/>
-      <c r="F12" s="38" t="s">
-        <v>15</v>
-      </c>
+      <c r="D12" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="48"/>
+      <c r="F12" s="48"/>
     </row>
-    <row r="13" spans="2:7" ht="38" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:7" ht="37.950000000000003" customHeight="1">
       <c r="B13" s="11"/>
       <c r="C13" s="9">
         <v>44839.59375</v>
       </c>
-      <c r="D13" s="36"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="39"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
     </row>
-    <row r="14" spans="2:7" ht="43" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B14" s="20"/>
+    <row r="14" spans="2:7" ht="43.05" customHeight="1" thickBot="1">
+      <c r="B14" s="16"/>
       <c r="C14" s="14">
         <v>44839.614583333336</v>
       </c>
-      <c r="D14" s="42" t="s">
+      <c r="D14" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
     </row>
-    <row r="15" spans="2:7" ht="89" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:7" ht="88.95" customHeight="1" thickBot="1">
       <c r="B15" s="11"/>
-      <c r="C15" s="9">
+      <c r="C15" s="24">
         <v>44839.635416666664</v>
       </c>
-      <c r="D15" s="40" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="F15" s="45"/>
+      <c r="D15" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="44"/>
     </row>
-    <row r="16" spans="2:7" ht="25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:7" ht="25.05" customHeight="1" thickBot="1">
       <c r="B16" s="11"/>
       <c r="C16" s="21">
         <v>0.67708333333333337</v>
       </c>
-      <c r="D16" s="41"/>
-      <c r="E16" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" s="26"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="41" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="17" spans="2:6" ht="75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6" ht="75" customHeight="1" thickBot="1">
       <c r="B17" s="11"/>
       <c r="C17" s="21">
         <v>0.6875</v>
       </c>
-      <c r="D17" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="27"/>
-      <c r="F17" s="28"/>
+      <c r="D17" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="34"/>
+      <c r="F17" s="42"/>
     </row>
-    <row r="18" spans="2:6" ht="38" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6" ht="37.950000000000003" customHeight="1">
       <c r="B18" s="4"/>
       <c r="C18" s="3">
         <v>44839.708333333336</v>
       </c>
-      <c r="D18" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" s="32"/>
-      <c r="F18" s="33"/>
+      <c r="D18" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="23"/>
+      <c r="F18" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="D12:F13"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="D17:E17"/>
     <mergeCell ref="C1:D2"/>
-    <mergeCell ref="E16:F17"/>
     <mergeCell ref="E9:E10"/>
     <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D12:E13"/>
-    <mergeCell ref="F12:F13"/>
     <mergeCell ref="D15:D16"/>
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="D14:F14"/>

--- a/unit-0/paneltalk-agenda/agenda.xlsx
+++ b/unit-0/paneltalk-agenda/agenda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\CertCompScience\workshop1-3\unit-0\paneltalk-agenda\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C639764B-F324-42AB-836B-045C5CEE9835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AC1B456-6CCE-4F92-9C0C-DFEA414385AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-9660" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,67 +35,6 @@
   </si>
   <si>
     <t>2024 Class</t>
-  </si>
-  <si>
-    <t>Workshop Close_x000B_</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Devops - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFEFEFE"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Richard</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="14"/>
-        <color rgb="FFFEFEFE"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> and Jimmy (F02)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color indexed="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Industry Engagement - </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="14"/>
-        <color rgb="FFFEFEFE"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Joan</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color indexed="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (Auditorium)</t>
-    </r>
   </si>
   <si>
     <r>
@@ -153,9 +92,6 @@
     <t>Dr Margaret Tynan</t>
   </si>
   <si>
-    <t>Registration (Auditorium)</t>
-  </si>
-  <si>
     <t>2025 Cert Class</t>
   </si>
   <si>
@@ -195,13 +131,6 @@
     </r>
   </si>
   <si>
-    <t>Some sort of meet and greet actviity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer Systems and Networks (Caroline and Frank)
-</t>
-  </si>
-  <si>
     <t>Databases - Roseanne and Mary</t>
   </si>
   <si>
@@ -212,10 +141,6 @@
     <t>Project Status - Colm</t>
   </si>
   <si>
-    <t xml:space="preserve">
-Interview Intelligence: Humans, AI, and the Future of Hiring - Joan (TBD)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Online Learning Experience: Managing Expectations  -                                          Laura
 </t>
   </si>
@@ -224,6 +149,80 @@
   </si>
   <si>
     <t xml:space="preserve"> Workshop 1, 3 &amp; 5 -January 16th 2026</t>
+  </si>
+  <si>
+    <t>Group Actviity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer Systems and Networks (Caroline, Mujahid and Frank)
+</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Industry Engagement - </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color rgb="FFFEFEFE"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Joan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color indexed="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>Interview Intelligence: Humans, AI, and the Future of Hiring - Joan (TBD)</t>
+  </si>
+  <si>
+    <t>IT Hiring Workshop (TBD)</t>
+  </si>
+  <si>
+    <t>Workshop Close</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Devops                                                     </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFEFEFE"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Richard</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color rgb="FFFEFEFE"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> and Jimmy                              (F02)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color indexed="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -324,12 +323,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDFDA70"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFC979B"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -348,7 +341,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF002060"/>
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -532,14 +531,12 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -548,7 +545,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -579,15 +576,9 @@
     <xf numFmtId="20" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -600,94 +591,70 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="20" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="20" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -696,14 +663,38 @@
     <xf numFmtId="49" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -945,15 +936,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>2068830</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:colOff>1663065</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>87630</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>2533284</xdr:colOff>
+      <xdr:colOff>2131329</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>91440</xdr:rowOff>
+      <xdr:rowOff>552450</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -982,8 +973,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6355080" y="981075"/>
-          <a:ext cx="464454" cy="447675"/>
+          <a:off x="5949315" y="1430655"/>
+          <a:ext cx="468264" cy="461010"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -995,15 +986,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>2205990</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>390525</xdr:rowOff>
+      <xdr:colOff>2192655</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>131445</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>2670444</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:colOff>2651394</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>588645</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1032,8 +1023,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3729990" y="3895725"/>
-          <a:ext cx="464454" cy="453390"/>
+          <a:off x="3716655" y="2874645"/>
+          <a:ext cx="454929" cy="461010"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1044,23 +1035,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>989330</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>83820</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2263140</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>582930</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1463309</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2721879</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>1026795</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="Picture 21" descr="A white numbers on an orange background&#10;&#10;AI-generated content may be incorrect.">
+        <xdr:cNvPr id="23" name="Picture 22" descr="A white numbers on an orange background&#10;&#10;AI-generated content may be incorrect.">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA83024B-AE35-4E62-B157-8C13D8CB88EC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02166AB7-D031-4A3A-82B4-28AF1A9349E8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1082,58 +1073,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7923530" y="5674995"/>
-          <a:ext cx="477789" cy="468630"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2196465</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>769620</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2651394</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>97155</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="23" name="Picture 22" descr="A white numbers on an orange background&#10;&#10;AI-generated content may be incorrect.">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02166AB7-D031-4A3A-82B4-28AF1A9349E8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3720465" y="7894320"/>
-          <a:ext cx="460644" cy="461010"/>
+          <a:off x="3787140" y="7707630"/>
+          <a:ext cx="458739" cy="443865"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1145,65 +1086,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>1931670</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>453390</xdr:rowOff>
+      <xdr:colOff>2162175</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>87630</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>2417079</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>897255</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="Picture 23" descr="A white numbers on an orange background&#10;&#10;AI-generated content may be incorrect.">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FF679BE-E969-4F5B-B678-0730DA09F110}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6217920" y="9016365"/>
-          <a:ext cx="475884" cy="443865"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1590675</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>2036445</xdr:colOff>
+      <xdr:colOff>2611755</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>77470</xdr:rowOff>
+      <xdr:rowOff>553720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1226,8 +1117,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5876925" y="962025"/>
-          <a:ext cx="457200" cy="458470"/>
+          <a:off x="6448425" y="1430655"/>
+          <a:ext cx="445770" cy="462280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1239,15 +1130,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>2158365</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>201930</xdr:rowOff>
+      <xdr:colOff>2124075</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>131445</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>2611755</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>668020</xdr:rowOff>
+      <xdr:colOff>2573655</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>589915</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1270,8 +1161,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6444615" y="3707130"/>
-          <a:ext cx="461010" cy="462280"/>
+          <a:off x="6410325" y="2874645"/>
+          <a:ext cx="445770" cy="462280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1283,59 +1174,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>1497330</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:colOff>1792605</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>582930</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>1958340</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>22225</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="28" name="Picture 27">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA4F9E65-3C1C-4028-8C65-EACE4D6E70D1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8431530" y="5676900"/>
-          <a:ext cx="457200" cy="458470"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1762125</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>533400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>2225040</xdr:colOff>
+      <xdr:colOff>2257425</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>437515</xdr:rowOff>
+      <xdr:rowOff>1028065</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1358,8 +1205,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8696325" y="7115175"/>
-          <a:ext cx="457200" cy="458470"/>
+          <a:off x="8726805" y="7707630"/>
+          <a:ext cx="464820" cy="445135"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1371,15 +1218,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>2295525</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>2297430</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>131445</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>2758440</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>439420</xdr:rowOff>
+      <xdr:colOff>2762250</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>570865</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1402,8 +1249,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9229725" y="3505200"/>
-          <a:ext cx="457200" cy="439420"/>
+          <a:off x="9231630" y="2874645"/>
+          <a:ext cx="461010" cy="439420"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1412,62 +1259,146 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>2005965</xdr:colOff>
+      <xdr:colOff>989330</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>93345</xdr:rowOff>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>2459355</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>16510</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="32" name="Picture 31">
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="5" name="Group 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86F43DC2-0804-4D15-B675-499174D2603A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{786F5269-2A68-1793-3377-68BA8D5C1A74}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="8940165" y="5684520"/>
-          <a:ext cx="457200" cy="429895"/>
+          <a:off x="7923530" y="5678805"/>
+          <a:ext cx="1466215" cy="464820"/>
+          <a:chOff x="7923530" y="5676900"/>
+          <a:chExt cx="1470025" cy="466725"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="22" name="Picture 21" descr="A white numbers on an orange background&#10;&#10;AI-generated content may be incorrect.">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA83024B-AE35-4E62-B157-8C13D8CB88EC}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="7923530" y="5676900"/>
+            <a:ext cx="473979" cy="466725"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="28" name="Picture 27">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA4F9E65-3C1C-4028-8C65-EACE4D6E70D1}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="8435340" y="5678805"/>
+            <a:ext cx="457200" cy="448945"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="32" name="Picture 31">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86F43DC2-0804-4D15-B675-499174D2603A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="8936355" y="5688330"/>
+            <a:ext cx="457200" cy="433705"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>2247900</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>533400</xdr:rowOff>
+      <xdr:colOff>2335530</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>582930</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>2705100</xdr:colOff>
+      <xdr:colOff>2796540</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>435610</xdr:rowOff>
+      <xdr:rowOff>1026160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1490,8 +1421,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9182100" y="7115175"/>
-          <a:ext cx="457200" cy="439420"/>
+          <a:off x="9269730" y="7707630"/>
+          <a:ext cx="461010" cy="443230"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1503,15 +1434,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>2331720</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>154305</xdr:rowOff>
+      <xdr:colOff>2333625</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>87630</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>2779395</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>287020</xdr:rowOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>534670</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1534,8 +1465,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9265920" y="8402955"/>
-          <a:ext cx="447675" cy="433705"/>
+          <a:off x="9267825" y="1430655"/>
+          <a:ext cx="445770" cy="447040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1544,48 +1475,132 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1348740</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>472440</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>913130</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>234315</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1807845</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2383155</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>930910</xdr:rowOff>
+      <xdr:rowOff>381000</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="35" name="Picture 34">
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="6" name="Group 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{182A83A7-BE57-4F0B-BB97-5EC434986ADE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DAFB17F5-42FE-4788-B25B-BE00DC19D0F6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5634990" y="9035415"/>
-          <a:ext cx="459105" cy="458470"/>
+          <a:off x="7847330" y="8484870"/>
+          <a:ext cx="1466215" cy="459105"/>
+          <a:chOff x="7923530" y="5676900"/>
+          <a:chExt cx="1470025" cy="466725"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="7" name="Picture 6" descr="A white numbers on an orange background&#10;&#10;AI-generated content may be incorrect.">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C93FAEE-688E-ECC5-61F5-087562D7194B}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="7923530" y="5676900"/>
+            <a:ext cx="473979" cy="466725"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="8" name="Picture 7">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BAD1531-73D1-B8BD-A85A-D95B73A7D2BB}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="8435340" y="5678805"/>
+            <a:ext cx="457200" cy="448945"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="9" name="Picture 8">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBD64C71-8EAC-0D4B-A84F-2B13D04A5AF0}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="8936355" y="5688330"/>
+            <a:ext cx="457200" cy="433705"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2633,7 +2648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B1:G18"/>
+  <dimension ref="B1:J18"/>
   <sheetFormatPr defaultColWidth="16.33203125" defaultRowHeight="19.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4.77734375" style="1" customWidth="1"/>
@@ -2646,228 +2661,227 @@
     <col min="8" max="16384" width="16.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="13.95" customHeight="1">
-      <c r="C1" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" s="17"/>
+    <row r="1" spans="2:10" ht="13.95" customHeight="1">
+      <c r="C1" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="24"/>
     </row>
-    <row r="2" spans="2:7" ht="43.05" customHeight="1">
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
+    <row r="2" spans="2:10" ht="43.05" customHeight="1">
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
       <c r="F2" s="2" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="3" spans="2:7" ht="19.95" customHeight="1">
+    <row r="3" spans="2:10" ht="19.95" customHeight="1">
       <c r="B3" s="5"/>
       <c r="C3" s="6" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="2:7" ht="30" customHeight="1">
+    <row r="4" spans="2:10" ht="30" customHeight="1" thickBot="1">
       <c r="B4" s="8"/>
       <c r="C4" s="9">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D4" s="45" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="46"/>
-      <c r="F4" s="10"/>
+      <c r="D4" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
     </row>
-    <row r="5" spans="2:7" ht="46.05" customHeight="1">
-      <c r="B5" s="11"/>
+    <row r="5" spans="2:10" ht="46.05" customHeight="1">
+      <c r="B5" s="10"/>
       <c r="C5" s="9">
         <v>0.42708333333333331</v>
       </c>
-      <c r="D5" s="45" t="s">
+      <c r="D5" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="36"/>
+      <c r="F5" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="46"/>
-      <c r="F5" s="12"/>
     </row>
-    <row r="6" spans="2:7" ht="30" customHeight="1">
-      <c r="B6" s="11"/>
+    <row r="6" spans="2:10" ht="30" customHeight="1" thickBot="1">
+      <c r="B6" s="10"/>
       <c r="C6" s="9">
         <v>0.4375</v>
       </c>
-      <c r="D6" s="45" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="46"/>
-      <c r="F6" s="12"/>
+      <c r="D6" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="36"/>
+      <c r="F6" s="23"/>
     </row>
-    <row r="7" spans="2:7" ht="35.25" customHeight="1">
-      <c r="B7" s="13"/>
-      <c r="C7" s="14">
+    <row r="7" spans="2:10" ht="35.25" customHeight="1">
+      <c r="B7" s="11"/>
+      <c r="C7" s="12">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="20"/>
-      <c r="F7" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="20"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
     </row>
-    <row r="8" spans="2:7" ht="60" customHeight="1">
-      <c r="B8" s="15"/>
+    <row r="8" spans="2:10" ht="60" customHeight="1">
+      <c r="B8" s="13"/>
       <c r="C8" s="9">
         <v>0.47916666666666669</v>
       </c>
-      <c r="D8" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="35" t="s">
+      <c r="D8" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="38" t="s">
-        <v>9</v>
-      </c>
     </row>
-    <row r="9" spans="2:7" ht="60" customHeight="1">
-      <c r="B9" s="11"/>
+    <row r="9" spans="2:10" ht="60" customHeight="1">
+      <c r="B9" s="10"/>
       <c r="C9" s="9">
         <v>0.5</v>
       </c>
-      <c r="D9" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="39"/>
+      <c r="D9" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="34"/>
     </row>
-    <row r="10" spans="2:7" ht="49.95" customHeight="1">
-      <c r="B10" s="11"/>
+    <row r="10" spans="2:10" ht="49.95" customHeight="1">
+      <c r="B10" s="10"/>
       <c r="C10" s="9">
         <v>0.52083333333333337</v>
       </c>
-      <c r="D10" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="37"/>
-      <c r="F10" s="40" t="s">
-        <v>10</v>
+      <c r="D10" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="49"/>
+      <c r="F10" s="21" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="11" spans="2:7" ht="55.05" customHeight="1">
-      <c r="B11" s="13"/>
-      <c r="C11" s="14">
+    <row r="11" spans="2:10" ht="55.05" customHeight="1">
+      <c r="B11" s="11"/>
+      <c r="C11" s="12">
         <v>0.54166666666666663</v>
       </c>
-      <c r="D11" s="25" t="s">
+      <c r="D11" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
     </row>
-    <row r="12" spans="2:7" ht="40.950000000000003" customHeight="1">
-      <c r="B12" s="11"/>
+    <row r="12" spans="2:10" ht="40.950000000000003" customHeight="1">
+      <c r="B12" s="10"/>
       <c r="C12" s="9">
         <v>0.57291666666666663</v>
       </c>
-      <c r="D12" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="48"/>
-      <c r="F12" s="48"/>
+      <c r="D12" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
     </row>
-    <row r="13" spans="2:7" ht="37.950000000000003" customHeight="1">
-      <c r="B13" s="11"/>
+    <row r="13" spans="2:10" ht="37.950000000000003" customHeight="1">
+      <c r="B13" s="10"/>
       <c r="C13" s="9">
         <v>44839.59375</v>
       </c>
-      <c r="D13" s="49"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="J13" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="14" spans="2:7" ht="43.05" customHeight="1" thickBot="1">
-      <c r="B14" s="16"/>
-      <c r="C14" s="14">
+    <row r="14" spans="2:10" ht="43.05" customHeight="1" thickBot="1">
+      <c r="B14" s="14"/>
+      <c r="C14" s="12">
         <v>44839.614583333336</v>
       </c>
-      <c r="D14" s="25" t="s">
+      <c r="D14" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
     </row>
-    <row r="15" spans="2:7" ht="88.95" customHeight="1" thickBot="1">
-      <c r="B15" s="11"/>
-      <c r="C15" s="24">
+    <row r="15" spans="2:10" ht="88.95" customHeight="1" thickBot="1">
+      <c r="B15" s="10"/>
+      <c r="C15" s="16">
         <v>44839.635416666664</v>
       </c>
-      <c r="D15" s="31" t="s">
+      <c r="D15" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="43" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15" s="44"/>
+      <c r="F15" s="32"/>
     </row>
-    <row r="16" spans="2:7" ht="25.05" customHeight="1" thickBot="1">
-      <c r="B16" s="11"/>
-      <c r="C16" s="21">
+    <row r="16" spans="2:10" ht="25.05" customHeight="1">
+      <c r="B16" s="10"/>
+      <c r="C16" s="15">
         <v>0.67708333333333337</v>
       </c>
-      <c r="D16" s="32"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="41" t="s">
-        <v>21</v>
-      </c>
+      <c r="D16" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="46"/>
+      <c r="F16" s="46"/>
     </row>
-    <row r="17" spans="2:6" ht="75" customHeight="1" thickBot="1">
-      <c r="B17" s="11"/>
-      <c r="C17" s="21">
+    <row r="17" spans="2:6" ht="75" customHeight="1">
+      <c r="B17" s="10"/>
+      <c r="C17" s="15">
         <v>0.6875</v>
       </c>
-      <c r="D17" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="34"/>
-      <c r="F17" s="42"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
     </row>
     <row r="18" spans="2:6" ht="37.950000000000003" customHeight="1">
       <c r="B18" s="4"/>
       <c r="C18" s="3">
         <v>44839.708333333336</v>
       </c>
-      <c r="D18" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="E18" s="23"/>
-      <c r="F18" s="27"/>
+      <c r="D18" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="27"/>
+      <c r="F18" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="D12:F13"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="C1:D2"/>
-    <mergeCell ref="E9:E10"/>
+  <mergeCells count="14">
     <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D15:D16"/>
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="D14:F14"/>
     <mergeCell ref="E15:F15"/>
+    <mergeCell ref="D16:F17"/>
+    <mergeCell ref="D12:F13"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="C1:D2"/>
+    <mergeCell ref="E9:E10"/>
     <mergeCell ref="F8:F9"/>
-    <mergeCell ref="F7:G7"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="D7:G7"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup scale="70" orientation="portrait"/>

--- a/unit-0/paneltalk-agenda/agenda.xlsx
+++ b/unit-0/paneltalk-agenda/agenda.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\CertCompScience\workshop1-3\unit-0\paneltalk-agenda\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AC1B456-6CCE-4F92-9C0C-DFEA414385AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C70A37C9-A895-4A4B-80B6-0F6EAC516C5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-9660" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1-1 - Workshop 1, 3 &amp; 5 -" sheetId="3" r:id="rId1"/>
@@ -102,90 +102,13 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Welcome, Agenda and Introductions 
-</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Online Learning Experience - </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="14"/>
-        <color rgb="FFFEFEFE"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Laura</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color indexed="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-  </si>
-  <si>
-    <t>Databases - Roseanne and Mary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overview of Follow-on Courses
-</t>
-  </si>
-  <si>
-    <t>Project Status - Colm</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Online Learning Experience: Managing Expectations  -                                          Laura
-</t>
-  </si>
-  <si>
     <t>Cert/Higher Diploma in Computer Science</t>
   </si>
   <si>
     <t xml:space="preserve"> Workshop 1, 3 &amp; 5 -January 16th 2026</t>
   </si>
   <si>
-    <t>Group Actviity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer Systems and Networks (Caroline, Mujahid and Frank)
-</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Industry Engagement - </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="14"/>
-        <color rgb="FFFEFEFE"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Joan</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color indexed="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Interview Intelligence: Humans, AI, and the Future of Hiring - Joan (TBD)</t>
-  </si>
-  <si>
-    <t>IT Hiring Workshop (TBD)</t>
   </si>
   <si>
     <t>Workshop Close</t>
@@ -223,6 +146,90 @@
       <t xml:space="preserve">
 </t>
     </r>
+  </si>
+  <si>
+    <t>Computer Systems and Networks (Caroline, Mujahid and Frank)
+(F03)</t>
+  </si>
+  <si>
+    <t>Databases - Roseanne and Mary
+(Auditorium)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Online Learning Experience - </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color rgb="FFFEFEFE"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Laura</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color indexed="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(Auditorium)</t>
+    </r>
+  </si>
+  <si>
+    <t>Welcome, Agenda and Introductions 
+(Auditorium)</t>
+  </si>
+  <si>
+    <t>Project Status - Colm
+(F02)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Industry Engagement - </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color rgb="FFFEFEFE"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Joan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color indexed="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 
+(Auditorium)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> Online Learning Experience: Managing Expectations  -                                          Laura
+(F02)
+</t>
+  </si>
+  <si>
+    <t>IT Hiring Workshop
+(Auditorium)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overview of Follow-on Courses 
+(Auditorium)
+</t>
+  </si>
+  <si>
+    <t>Group Actviity
+(F03)</t>
   </si>
 </sst>
 </file>
@@ -323,12 +330,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFC979B"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFEFBC65"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -347,7 +348,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7A0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -609,13 +616,43 @@
     <xf numFmtId="49" fontId="5" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -624,49 +661,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -675,25 +679,28 @@
     <xf numFmtId="49" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -770,6 +777,7 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
     <mruColors>
+      <color rgb="FFFFC7A0"/>
       <color rgb="FF95CA73"/>
       <color rgb="FF7275A7"/>
       <color rgb="FFEFBC65"/>
@@ -777,7 +785,6 @@
       <color rgb="FFDFDA70"/>
       <color rgb="FF5BA4BB"/>
       <color rgb="FF8F6B9F"/>
-      <color rgb="FFFFC7A0"/>
       <color rgb="FFFF2600"/>
       <color rgb="FF942092"/>
     </mruColors>
@@ -1218,15 +1225,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>2297430</xdr:colOff>
+      <xdr:colOff>2305050</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>131445</xdr:rowOff>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>2762250</xdr:colOff>
+      <xdr:colOff>2769870</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>570865</xdr:rowOff>
+      <xdr:rowOff>487045</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1249,8 +1256,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9231630" y="2874645"/>
-          <a:ext cx="461010" cy="439420"/>
+          <a:off x="9246870" y="2798445"/>
+          <a:ext cx="464820" cy="439420"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1285,8 +1292,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7923530" y="5678805"/>
-          <a:ext cx="1466215" cy="464820"/>
+          <a:off x="7928148" y="5685270"/>
+          <a:ext cx="1470025" cy="471921"/>
           <a:chOff x="7923530" y="5676900"/>
           <a:chExt cx="1470025" cy="466725"/>
         </a:xfrm>
@@ -1501,8 +1508,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7847330" y="8484870"/>
-          <a:ext cx="1466215" cy="459105"/>
+          <a:off x="7851948" y="8512406"/>
+          <a:ext cx="1470025" cy="458412"/>
           <a:chOff x="7923530" y="5676900"/>
           <a:chExt cx="1470025" cy="466725"/>
         </a:xfrm>
@@ -2662,16 +2669,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="13.95" customHeight="1">
-      <c r="C1" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="24"/>
+      <c r="C1" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="34"/>
     </row>
     <row r="2" spans="2:10" ht="43.05" customHeight="1">
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
       <c r="F2" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="2:10" ht="19.95" customHeight="1">
@@ -2694,23 +2701,23 @@
       <c r="C4" s="9">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
     </row>
     <row r="5" spans="2:10" ht="46.05" customHeight="1">
       <c r="B5" s="10"/>
       <c r="C5" s="9">
         <v>0.42708333333333331</v>
       </c>
-      <c r="D5" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="36"/>
-      <c r="F5" s="22" t="s">
-        <v>15</v>
+      <c r="D5" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="37"/>
+      <c r="F5" s="45" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="2:10" ht="30" customHeight="1" thickBot="1">
@@ -2718,23 +2725,23 @@
       <c r="C6" s="9">
         <v>0.4375</v>
       </c>
-      <c r="D6" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="36"/>
-      <c r="F6" s="23"/>
+      <c r="D6" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="37"/>
+      <c r="F6" s="46"/>
     </row>
     <row r="7" spans="2:10" ht="35.25" customHeight="1">
       <c r="B7" s="11"/>
       <c r="C7" s="12">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D7" s="41" t="s">
+      <c r="D7" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
     </row>
     <row r="8" spans="2:10" ht="60" customHeight="1">
       <c r="B8" s="13"/>
@@ -2742,12 +2749,12 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="33" t="s">
+      <c r="E8" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="47" t="s">
         <v>6</v>
       </c>
     </row>
@@ -2757,12 +2764,12 @@
         <v>0.5</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="48" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="34"/>
+      <c r="F9" s="48"/>
     </row>
     <row r="10" spans="2:10" ht="49.95" customHeight="1">
       <c r="B10" s="10"/>
@@ -2770,10 +2777,10 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="49"/>
-      <c r="F10" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="44"/>
+      <c r="F10" s="49" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2782,33 +2789,33 @@
       <c r="C11" s="12">
         <v>0.54166666666666663</v>
       </c>
-      <c r="D11" s="29" t="s">
+      <c r="D11" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
     </row>
     <row r="12" spans="2:10" ht="40.950000000000003" customHeight="1">
       <c r="B12" s="10"/>
       <c r="C12" s="9">
         <v>0.57291666666666663</v>
       </c>
-      <c r="D12" s="37" t="s">
+      <c r="D12" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
     </row>
     <row r="13" spans="2:10" ht="37.950000000000003" customHeight="1">
       <c r="B13" s="10"/>
       <c r="C13" s="9">
         <v>44839.59375</v>
       </c>
-      <c r="D13" s="43"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="44"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
       <c r="J13" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="2:10" ht="43.05" customHeight="1" thickBot="1">
@@ -2816,11 +2823,11 @@
       <c r="C14" s="12">
         <v>44839.614583333336</v>
       </c>
-      <c r="D14" s="29" t="s">
+      <c r="D14" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
     </row>
     <row r="15" spans="2:10" ht="88.95" customHeight="1" thickBot="1">
       <c r="B15" s="10"/>
@@ -2828,52 +2835,46 @@
         <v>44839.635416666664</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="F15" s="32"/>
+      <c r="F15" s="27"/>
     </row>
     <row r="16" spans="2:10" ht="25.05" customHeight="1">
       <c r="B16" s="10"/>
       <c r="C16" s="15">
         <v>0.67708333333333337</v>
       </c>
-      <c r="D16" s="45" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="46"/>
-      <c r="F16" s="46"/>
+      <c r="D16" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
     </row>
     <row r="17" spans="2:6" ht="75" customHeight="1">
       <c r="B17" s="10"/>
       <c r="C17" s="15">
         <v>0.6875</v>
       </c>
-      <c r="D17" s="45"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="46"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
     </row>
     <row r="18" spans="2:6" ht="37.950000000000003" customHeight="1">
       <c r="B18" s="4"/>
       <c r="C18" s="3">
         <v>44839.708333333336</v>
       </c>
-      <c r="D18" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="27"/>
-      <c r="F18" s="28"/>
+      <c r="D18" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="22"/>
+      <c r="F18" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="D16:F17"/>
-    <mergeCell ref="D12:F13"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="C1:D2"/>
     <mergeCell ref="E9:E10"/>
@@ -2882,6 +2883,12 @@
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="D7:G7"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="D16:F17"/>
+    <mergeCell ref="D12:F13"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup scale="70" orientation="portrait"/>

--- a/unit-0/paneltalk-agenda/agenda.xlsx
+++ b/unit-0/paneltalk-agenda/agenda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\CertCompScience\workshop1-3\unit-0\paneltalk-agenda\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C70A37C9-A895-4A4B-80B6-0F6EAC516C5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB9CF0C-4EA8-4E9F-82A2-F379EE298707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -359,7 +359,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -489,32 +489,6 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -538,11 +512,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left/>
+      <right/>
+      <top style="medium">
         <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -552,7 +526,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -562,9 +536,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -613,8 +584,56 @@
     <xf numFmtId="49" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -631,15 +650,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -655,53 +665,14 @@
     <xf numFmtId="49" fontId="5" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="21" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1482,134 +1453,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>913130</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>234315</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>2383155</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>381000</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="6" name="Group 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DAFB17F5-42FE-4788-B25B-BE00DC19D0F6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="7851948" y="8512406"/>
-          <a:ext cx="1470025" cy="458412"/>
-          <a:chOff x="7923530" y="5676900"/>
-          <a:chExt cx="1470025" cy="466725"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="7" name="Picture 6" descr="A white numbers on an orange background&#10;&#10;AI-generated content may be incorrect.">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C93FAEE-688E-ECC5-61F5-087562D7194B}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print">
-            <a:extLst>
-              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-              </a:ext>
-            </a:extLst>
-          </a:blip>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="7923530" y="5676900"/>
-            <a:ext cx="473979" cy="466725"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="8" name="Picture 7">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BAD1531-73D1-B8BD-A85A-D95B73A7D2BB}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="8435340" y="5678805"/>
-            <a:ext cx="457200" cy="448945"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="9" name="Picture 8">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBD64C71-8EAC-0D4B-A84F-2B13D04A5AF0}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="8936355" y="5688330"/>
-            <a:ext cx="457200" cy="433705"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2669,212 +2512,216 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="13.95" customHeight="1">
-      <c r="C1" s="34" t="s">
+      <c r="C1" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="34"/>
+      <c r="D1" s="24"/>
     </row>
     <row r="2" spans="2:10" ht="43.05" customHeight="1">
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
       <c r="F2" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="2:10" ht="19.95" customHeight="1">
-      <c r="B3" s="5"/>
-      <c r="C3" s="6" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="2:10" ht="30" customHeight="1" thickBot="1">
-      <c r="B4" s="8"/>
-      <c r="C4" s="9">
+      <c r="B4" s="7"/>
+      <c r="C4" s="8">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D4" s="38" t="s">
+      <c r="D4" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
     </row>
     <row r="5" spans="2:10" ht="46.05" customHeight="1">
-      <c r="B5" s="10"/>
-      <c r="C5" s="9">
+      <c r="B5" s="9"/>
+      <c r="C5" s="8">
         <v>0.42708333333333331</v>
       </c>
-      <c r="D5" s="36" t="s">
+      <c r="D5" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="37"/>
-      <c r="F5" s="45" t="s">
+      <c r="E5" s="31"/>
+      <c r="F5" s="22" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="2:10" ht="30" customHeight="1" thickBot="1">
-      <c r="B6" s="10"/>
-      <c r="C6" s="9">
+      <c r="B6" s="9"/>
+      <c r="C6" s="8">
         <v>0.4375</v>
       </c>
-      <c r="D6" s="36" t="s">
+      <c r="D6" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="37"/>
-      <c r="F6" s="46"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="23"/>
     </row>
     <row r="7" spans="2:10" ht="35.25" customHeight="1">
-      <c r="B7" s="11"/>
-      <c r="C7" s="12">
+      <c r="B7" s="10"/>
+      <c r="C7" s="11">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D7" s="40" t="s">
+      <c r="D7" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
     </row>
     <row r="8" spans="2:10" ht="60" customHeight="1">
-      <c r="B8" s="13"/>
-      <c r="C8" s="9">
+      <c r="B8" s="12"/>
+      <c r="C8" s="8">
         <v>0.47916666666666669</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="42" t="s">
+      <c r="E8" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="47" t="s">
+      <c r="F8" s="28" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="2:10" ht="60" customHeight="1">
-      <c r="B9" s="10"/>
-      <c r="C9" s="9">
+      <c r="B9" s="9"/>
+      <c r="C9" s="8">
         <v>0.5</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="43" t="s">
+      <c r="E9" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="48"/>
+      <c r="F9" s="29"/>
     </row>
     <row r="10" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B10" s="10"/>
-      <c r="C10" s="9">
+      <c r="B10" s="9"/>
+      <c r="C10" s="8">
         <v>0.52083333333333337</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="44"/>
-      <c r="F10" s="49" t="s">
+      <c r="E10" s="27"/>
+      <c r="F10" s="21" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="2:10" ht="55.05" customHeight="1">
-      <c r="B11" s="11"/>
-      <c r="C11" s="12">
+      <c r="B11" s="10"/>
+      <c r="C11" s="11">
         <v>0.54166666666666663</v>
       </c>
-      <c r="D11" s="24" t="s">
+      <c r="D11" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
     </row>
     <row r="12" spans="2:10" ht="40.950000000000003" customHeight="1">
-      <c r="B12" s="10"/>
-      <c r="C12" s="9">
+      <c r="B12" s="9"/>
+      <c r="C12" s="8">
         <v>0.57291666666666663</v>
       </c>
-      <c r="D12" s="30" t="s">
+      <c r="D12" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
     </row>
     <row r="13" spans="2:10" ht="37.950000000000003" customHeight="1">
-      <c r="B13" s="10"/>
-      <c r="C13" s="9">
+      <c r="B13" s="9"/>
+      <c r="C13" s="8">
         <v>44839.59375</v>
       </c>
-      <c r="D13" s="32"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
       <c r="J13" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="14" spans="2:10" ht="43.05" customHeight="1" thickBot="1">
-      <c r="B14" s="14"/>
-      <c r="C14" s="12">
+      <c r="B14" s="13"/>
+      <c r="C14" s="11">
         <v>44839.614583333336</v>
       </c>
-      <c r="D14" s="24" t="s">
+      <c r="D14" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
     </row>
-    <row r="15" spans="2:10" ht="88.95" customHeight="1" thickBot="1">
-      <c r="B15" s="10"/>
-      <c r="C15" s="16">
+    <row r="15" spans="2:10" ht="88.95" customHeight="1">
+      <c r="B15" s="9"/>
+      <c r="C15" s="15">
         <v>44839.635416666664</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="E15" s="26" t="s">
+      <c r="E15" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="F15" s="27"/>
+      <c r="F15" s="46"/>
     </row>
     <row r="16" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B16" s="10"/>
-      <c r="C16" s="15">
-        <v>0.67708333333333337</v>
-      </c>
-      <c r="D16" s="28" t="s">
+      <c r="B16" s="9"/>
+      <c r="C16" s="14">
+        <v>0.65625</v>
+      </c>
+      <c r="D16" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
     </row>
-    <row r="17" spans="2:6" ht="75" customHeight="1">
-      <c r="B17" s="10"/>
-      <c r="C17" s="15">
-        <v>0.6875</v>
-      </c>
-      <c r="D17" s="28"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="29"/>
+    <row r="17" spans="2:6" ht="55.2" customHeight="1">
+      <c r="B17" s="9"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="47"/>
     </row>
     <row r="18" spans="2:6" ht="37.950000000000003" customHeight="1">
-      <c r="B18" s="4"/>
-      <c r="C18" s="3">
-        <v>44839.708333333336</v>
-      </c>
-      <c r="D18" s="21" t="s">
+      <c r="B18" s="3"/>
+      <c r="C18" s="48">
+        <v>0.6875</v>
+      </c>
+      <c r="D18" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="22"/>
-      <c r="F18" s="23"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D12:F13"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E15:F17"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="C1:D2"/>
     <mergeCell ref="E9:E10"/>
@@ -2883,12 +2730,6 @@
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="D7:G7"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="D16:F17"/>
-    <mergeCell ref="D12:F13"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup scale="70" orientation="portrait"/>

--- a/unit-0/paneltalk-agenda/agenda.xlsx
+++ b/unit-0/paneltalk-agenda/agenda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\CertCompScience\workshop1-3\unit-0\paneltalk-agenda\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB9CF0C-4EA8-4E9F-82A2-F379EE298707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{748F0481-BF21-4E92-B75B-03CF344613F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -148,10 +148,6 @@
     </r>
   </si>
   <si>
-    <t>Computer Systems and Networks (Caroline, Mujahid and Frank)
-(F03)</t>
-  </si>
-  <si>
     <t>Databases - Roseanne and Mary
 (Auditorium)</t>
   </si>
@@ -214,22 +210,26 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve"> Online Learning Experience: Managing Expectations  -                                          Laura
-(F02)
-</t>
-  </si>
-  <si>
-    <t>IT Hiring Workshop
-(Auditorium)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Overview of Follow-on Courses 
 (Auditorium)
 </t>
   </si>
   <si>
+    <t xml:space="preserve"> Online Learning Experience: Managing Expectations  -                                          Laura
+(Auditorium)
+</t>
+  </si>
+  <si>
+    <t>IT Hiring Workshop
+(F02)</t>
+  </si>
+  <si>
     <t>Group Actviity
-(F03)</t>
+(Atrium)</t>
+  </si>
+  <si>
+    <t>Computer Systems and Networks (Caroline, Mujahid and Frank)
+(Auditorium)</t>
   </si>
 </sst>
 </file>
@@ -359,7 +359,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -520,13 +520,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -593,6 +604,42 @@
     <xf numFmtId="49" fontId="5" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="21" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -635,44 +682,11 @@
     <xf numFmtId="49" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="21" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2512,14 +2526,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="13.95" customHeight="1">
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="24"/>
+      <c r="D1" s="36"/>
     </row>
     <row r="2" spans="2:10" ht="43.05" customHeight="1">
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
       <c r="F2" s="2" t="s">
         <v>12</v>
       </c>
@@ -2544,23 +2558,23 @@
       <c r="C4" s="8">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
     </row>
     <row r="5" spans="2:10" ht="46.05" customHeight="1">
       <c r="B5" s="9"/>
       <c r="C5" s="8">
         <v>0.42708333333333331</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="43"/>
+      <c r="F5" s="34" t="s">
         <v>19</v>
-      </c>
-      <c r="E5" s="31"/>
-      <c r="F5" s="22" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="6" spans="2:10" ht="30" customHeight="1" thickBot="1">
@@ -2568,23 +2582,23 @@
       <c r="C6" s="8">
         <v>0.4375</v>
       </c>
-      <c r="D6" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="31"/>
-      <c r="F6" s="23"/>
+      <c r="D6" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="43"/>
+      <c r="F6" s="35"/>
     </row>
     <row r="7" spans="2:10" ht="35.25" customHeight="1">
       <c r="B7" s="10"/>
       <c r="C7" s="11">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D7" s="34" t="s">
+      <c r="D7" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
+      <c r="E7" s="47"/>
+      <c r="F7" s="47"/>
+      <c r="G7" s="47"/>
     </row>
     <row r="8" spans="2:10" ht="60" customHeight="1">
       <c r="B8" s="12"/>
@@ -2592,12 +2606,12 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="28" t="s">
+      <c r="F8" s="40" t="s">
         <v>6</v>
       </c>
     </row>
@@ -2607,12 +2621,12 @@
         <v>0.5</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="29"/>
+      <c r="F9" s="41"/>
     </row>
     <row r="10" spans="2:10" ht="49.95" customHeight="1">
       <c r="B10" s="9"/>
@@ -2620,9 +2634,9 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="27"/>
+        <v>16</v>
+      </c>
+      <c r="E10" s="39"/>
       <c r="F10" s="21" t="s">
         <v>7</v>
       </c>
@@ -2632,31 +2646,31 @@
       <c r="C11" s="11">
         <v>0.54166666666666663</v>
       </c>
-      <c r="D11" s="39" t="s">
+      <c r="D11" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
     </row>
     <row r="12" spans="2:10" ht="40.950000000000003" customHeight="1">
       <c r="B12" s="9"/>
       <c r="C12" s="8">
         <v>0.57291666666666663</v>
       </c>
-      <c r="D12" s="42" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
+      <c r="D12" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
     </row>
     <row r="13" spans="2:10" ht="37.950000000000003" customHeight="1">
       <c r="B13" s="9"/>
       <c r="C13" s="8">
         <v>44839.59375</v>
       </c>
-      <c r="D13" s="44"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
       <c r="J13" s="1" t="s">
         <v>13</v>
       </c>
@@ -2666,13 +2680,13 @@
       <c r="C14" s="11">
         <v>44839.614583333336</v>
       </c>
-      <c r="D14" s="39" t="s">
+      <c r="D14" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
     </row>
-    <row r="15" spans="2:10" ht="88.95" customHeight="1">
+    <row r="15" spans="2:10" ht="88.95" customHeight="1" thickBot="1">
       <c r="B15" s="9"/>
       <c r="C15" s="15">
         <v>44839.635416666664</v>
@@ -2680,48 +2694,42 @@
       <c r="D15" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="E15" s="46" t="s">
+      <c r="E15" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="F15" s="46"/>
+      <c r="F15" s="32"/>
     </row>
     <row r="16" spans="2:10" ht="25.05" customHeight="1">
       <c r="B16" s="9"/>
       <c r="C16" s="14">
         <v>0.65625</v>
       </c>
-      <c r="D16" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="47"/>
-      <c r="F16" s="47"/>
+      <c r="D16" s="48" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
     </row>
     <row r="17" spans="2:6" ht="55.2" customHeight="1">
       <c r="B17" s="9"/>
       <c r="C17" s="14"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="47"/>
-      <c r="F17" s="47"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
     </row>
     <row r="18" spans="2:6" ht="37.950000000000003" customHeight="1">
       <c r="B18" s="3"/>
-      <c r="C18" s="48">
+      <c r="C18" s="22">
         <v>0.6875</v>
       </c>
-      <c r="D18" s="36" t="s">
+      <c r="D18" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="37"/>
-      <c r="F18" s="38"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D12:F13"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E15:F17"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="C1:D2"/>
     <mergeCell ref="E9:E10"/>
@@ -2730,6 +2738,12 @@
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="D7:G7"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D12:F13"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E15:F17"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup scale="70" orientation="portrait"/>

--- a/unit-0/paneltalk-agenda/agenda.xlsx
+++ b/unit-0/paneltalk-agenda/agenda.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\CertCompScience\2026\workshop1Sept\unit-0\paneltalk-agenda\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF5B4129-AA23-4B47-8A2A-B391A17BD5B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{066867AE-5E84-4B17-A010-C56D25676B0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="42">
   <si>
     <t>Time</t>
   </si>
@@ -181,63 +181,89 @@
 </t>
   </si>
   <si>
-    <t>Online Learning Experience - Laura</t>
-  </si>
-  <si>
-    <t>Web Dev - John Rellis</t>
-  </si>
-  <si>
     <t>Slack Overview - Importance of Communication</t>
   </si>
   <si>
-    <t>Getting Help and Staying Connected with Slack - Colm</t>
-  </si>
-  <si>
-    <t>AI Module 2 - Tamas</t>
+    <t>Online Learning Experience - Laura McGibney(F01)</t>
+  </si>
+  <si>
+    <t>Welcome, Agenda and Introductions 
+(G17)
+Siobhan Roche &amp; Dr. Frank Walsh</t>
   </si>
   <si>
     <t xml:space="preserve">Getting to know the Tutors Stack
 (G17)
-Colm &amp; Pete
+Colm Dunphy &amp; Pete Windle
 </t>
   </si>
   <si>
-    <t>Welcome, Agenda and Introductions 
-(G17)
-Siobhan &amp; Frank</t>
-  </si>
-  <si>
-    <t>Online Learning Experience - Laura (F01)</t>
-  </si>
-  <si>
-    <t>Getting Help and Staying Connected with Slack - Colm (F02)</t>
-  </si>
-  <si>
-    <t>AI Module 1 - Indrakshi  (F03)</t>
-  </si>
-  <si>
-    <t>Getting Help and Staying Connected with Slack- Colm (F01)</t>
-  </si>
-  <si>
-    <t>Devops                                                     Richard and Jimmy   (F02)</t>
-  </si>
-  <si>
-    <t>Online Learning Experience - Laura (F03)</t>
+    <t>Getting Help and Staying Connected with Slack - Colm Dunphy (F02)</t>
+  </si>
+  <si>
+    <t>Getting Help and Staying Connected with Slack - Colm Dunphy (E19B)</t>
+  </si>
+  <si>
+    <t>Online Learning Experience - Laura Mc Gibney (E19B)</t>
+  </si>
+  <si>
+    <t>The Evolution of Machine Learning and AI - Indrakshi Dey  (F02)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Full Stack  - </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color rgb="FFFEFEFE"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Eamonn deLeastar and Frank Walsh
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color indexed="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Online Learning Experience - Laura McGibney (F02)</t>
+  </si>
+  <si>
+    <t>Data Handling and Infrastructure for AI - Tamas Grotz, Abdul Wahid.</t>
+  </si>
+  <si>
+    <t>Web Dev - John Rellis (F01)</t>
+  </si>
+  <si>
+    <t>WorkShop 
+- Bring your laptop and get help with software installation
+(IT119)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Importance of Community - Laura McGibney 
+Reflection on Day - Chance to ask questions - Team (G17)
+</t>
+  </si>
+  <si>
+    <t>Devops                                                     Richard Frisby and Jimmy McGibney (E19B)</t>
+  </si>
+  <si>
+    <t>Getting Help and Staying Connected with Slack- Colm Dunphy(F01)</t>
   </si>
   <si>
     <t>Python Programming WorkShop 
  - Bring your laptop and get help with software installation  (IT118)
-Siobhan &amp; Mairead</t>
-  </si>
-  <si>
-    <t>Moving from Java to Python WorkShop 
-- Bring your laptop and get help with software installation
-(IT119)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Importance of Community - Laura 
-Reflection on Day - Chance to ask questions - All (G17)
-</t>
+Siobhan Roche &amp; Mairead Meagher</t>
   </si>
 </sst>
 </file>
@@ -676,6 +702,78 @@
     <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -688,76 +786,31 @@
     <xf numFmtId="49" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -774,33 +827,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1961,14 +1987,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" ht="13.95" customHeight="1">
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="24"/>
+      <c r="D1" s="48"/>
     </row>
     <row r="2" spans="2:14" ht="43.2" customHeight="1">
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
       <c r="F2" s="2" t="s">
         <v>12</v>
       </c>
@@ -1993,50 +2019,50 @@
       <c r="C4" s="8">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
     </row>
     <row r="5" spans="2:14" ht="64.2" customHeight="1">
       <c r="B5" s="9"/>
       <c r="C5" s="8">
         <v>0.42708333333333331</v>
       </c>
-      <c r="D5" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="29"/>
-      <c r="F5" s="30"/>
+      <c r="D5" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="31"/>
+      <c r="F5" s="32"/>
     </row>
     <row r="6" spans="2:14" ht="64.8" customHeight="1">
       <c r="B6" s="9"/>
       <c r="C6" s="8">
         <v>0.4375</v>
       </c>
-      <c r="D6" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="29"/>
-      <c r="F6" s="30"/>
-      <c r="K6" s="28" t="s">
+      <c r="D6" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="31"/>
+      <c r="F6" s="32"/>
+      <c r="K6" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="L6" s="29"/>
-      <c r="M6" s="30"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="32"/>
     </row>
     <row r="7" spans="2:14" ht="35.25" customHeight="1">
       <c r="B7" s="10"/>
       <c r="C7" s="11">
         <v>0.46875</v>
       </c>
-      <c r="D7" s="31" t="s">
+      <c r="D7" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="33"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="39"/>
     </row>
     <row r="8" spans="2:14" ht="44.25" customHeight="1">
       <c r="B8" s="12"/>
@@ -2044,21 +2070,24 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="2:14" ht="7.8" customHeight="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" ht="18">
       <c r="B9" s="9"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="33"/>
+      <c r="C9" s="15">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="D9" s="37"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="39"/>
     </row>
     <row r="10" spans="2:14" ht="37.5" customHeight="1">
       <c r="B10" s="9"/>
@@ -2069,44 +2098,44 @@
         <v>26</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F10" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="L10" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="L10" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="M10" s="35"/>
-      <c r="N10" s="35"/>
+      <c r="M10" s="41"/>
+      <c r="N10" s="41"/>
     </row>
     <row r="11" spans="2:14" ht="55.2" customHeight="1">
       <c r="B11" s="10"/>
       <c r="C11" s="11">
         <v>0.54166666666666663</v>
       </c>
-      <c r="D11" s="36" t="s">
+      <c r="D11" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
-    </row>
-    <row r="12" spans="2:14" ht="40.950000000000003" customHeight="1">
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+    </row>
+    <row r="12" spans="2:14" ht="66" customHeight="1">
       <c r="B12" s="9"/>
       <c r="C12" s="15">
         <v>0.57291666666666663</v>
       </c>
-      <c r="D12" s="51" t="s">
-        <v>35</v>
+      <c r="D12" s="36" t="s">
+        <v>40</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F12" s="23" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="2:14" ht="48" customHeight="1">
@@ -2114,75 +2143,85 @@
       <c r="C13" s="15">
         <v>44839.59375</v>
       </c>
-      <c r="D13" s="51"/>
-      <c r="E13" s="38" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" s="39" t="s">
-        <v>29</v>
+      <c r="D13" s="36"/>
+      <c r="E13" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="45" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="2:14" ht="24" hidden="1" customHeight="1">
       <c r="B14" s="9"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="39"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="45"/>
     </row>
     <row r="15" spans="2:14" ht="43.2" customHeight="1">
       <c r="B15" s="13"/>
       <c r="C15" s="11">
         <v>44839.614583333336</v>
       </c>
-      <c r="D15" s="40" t="s">
+      <c r="D15" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
     </row>
     <row r="16" spans="2:14" ht="88.95" customHeight="1">
       <c r="B16" s="9"/>
       <c r="C16" s="15">
         <v>44839.635416666664</v>
       </c>
-      <c r="D16" s="42" t="s">
-        <v>38</v>
-      </c>
-      <c r="E16" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16" s="45"/>
+      <c r="D16" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" s="27"/>
     </row>
     <row r="17" spans="2:6" ht="1.8" customHeight="1">
       <c r="B17" s="9"/>
       <c r="C17" s="14"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="47"/>
-    </row>
-    <row r="18" spans="2:6" ht="49.8" customHeight="1">
+      <c r="D17" s="25"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="29"/>
+    </row>
+    <row r="18" spans="2:6" ht="60" customHeight="1">
       <c r="B18" s="9"/>
       <c r="C18" s="14">
         <v>0.66666666666666663</v>
       </c>
-      <c r="D18" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="E18" s="29"/>
-      <c r="F18" s="30"/>
+      <c r="D18" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" s="31"/>
+      <c r="F18" s="32"/>
     </row>
     <row r="19" spans="2:6" ht="37.950000000000003" customHeight="1">
       <c r="B19" s="3"/>
       <c r="C19" s="19">
         <v>0.6875</v>
       </c>
-      <c r="D19" s="48" t="s">
+      <c r="D19" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="E19" s="49"/>
-      <c r="F19" s="50"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="C1:D2"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="D15:F15"/>
     <mergeCell ref="D16:D17"/>
     <mergeCell ref="E16:F17"/>
     <mergeCell ref="D18:F18"/>
@@ -2190,16 +2229,6 @@
     <mergeCell ref="D6:F6"/>
     <mergeCell ref="D12:D14"/>
     <mergeCell ref="D9:G9"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="C1:D2"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="D7:G7"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup scale="70" orientation="portrait"/>
@@ -2225,14 +2254,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="13.95" customHeight="1">
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="24"/>
+      <c r="D1" s="48"/>
     </row>
     <row r="2" spans="2:7" ht="43.2" customHeight="1">
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
       <c r="F2" s="2" t="s">
         <v>12</v>
       </c>
@@ -2257,83 +2286,83 @@
       <c r="C4" s="8">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
     </row>
     <row r="5" spans="2:7" ht="46.2" customHeight="1">
       <c r="B5" s="9"/>
       <c r="C5" s="8">
         <v>0.42708333333333331</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="29"/>
-      <c r="F5" s="30"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="32"/>
     </row>
     <row r="6" spans="2:7" ht="43.5" customHeight="1">
       <c r="B6" s="9"/>
       <c r="C6" s="8">
         <v>0.4375</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="29"/>
-      <c r="F6" s="30"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="32"/>
     </row>
     <row r="7" spans="2:7" ht="35.25" customHeight="1">
       <c r="B7" s="10"/>
       <c r="C7" s="11">
         <v>0.46875</v>
       </c>
-      <c r="D7" s="62" t="s">
+      <c r="D7" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
     </row>
     <row r="8" spans="2:7" ht="44.25" customHeight="1">
       <c r="B8" s="12"/>
       <c r="C8" s="8">
         <v>0.48958333333333331</v>
       </c>
-      <c r="D8" s="28" t="s">
+      <c r="D8" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="29"/>
-      <c r="F8" s="30"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="32"/>
     </row>
     <row r="9" spans="2:7" ht="29.25" customHeight="1">
       <c r="B9" s="9"/>
       <c r="C9" s="8"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="59"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="54"/>
     </row>
     <row r="10" spans="2:7" ht="37.5" customHeight="1">
       <c r="B10" s="9"/>
       <c r="C10" s="8"/>
-      <c r="D10" s="34" t="s">
+      <c r="D10" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
     </row>
     <row r="11" spans="2:7" ht="55.2" customHeight="1" thickBot="1">
       <c r="B11" s="10"/>
       <c r="C11" s="11">
         <v>0.54166666666666663</v>
       </c>
-      <c r="D11" s="55" t="s">
+      <c r="D11" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="56"/>
-      <c r="F11" s="56"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="65"/>
     </row>
     <row r="12" spans="2:7" ht="40.950000000000003" customHeight="1" thickBot="1">
       <c r="B12" s="9"/>
@@ -2355,84 +2384,90 @@
       <c r="C13" s="8">
         <v>44839.59375</v>
       </c>
-      <c r="D13" s="60" t="s">
+      <c r="D13" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="63" t="s">
+      <c r="E13" s="58" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="65" t="s">
+      <c r="F13" s="60" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="24" hidden="1" customHeight="1">
       <c r="B14" s="9"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="65"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="59"/>
+      <c r="F14" s="60"/>
     </row>
     <row r="15" spans="2:7" ht="43.2" customHeight="1">
       <c r="B15" s="13"/>
       <c r="C15" s="11">
         <v>44839.614583333336</v>
       </c>
-      <c r="D15" s="40" t="s">
+      <c r="D15" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
     </row>
     <row r="16" spans="2:7" ht="88.95" customHeight="1">
       <c r="B16" s="9"/>
       <c r="C16" s="15">
         <v>44839.635416666664</v>
       </c>
-      <c r="D16" s="42" t="s">
+      <c r="D16" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="44" t="s">
+      <c r="E16" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="F16" s="45"/>
+      <c r="F16" s="27"/>
     </row>
     <row r="17" spans="2:6" ht="25.2" customHeight="1">
       <c r="B17" s="9"/>
       <c r="C17" s="14"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="52"/>
-      <c r="F17" s="53"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="61"/>
+      <c r="F17" s="62"/>
     </row>
     <row r="18" spans="2:6" ht="55.2" customHeight="1">
       <c r="B18" s="9"/>
       <c r="C18" s="14"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="47"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="29"/>
     </row>
     <row r="19" spans="2:6" ht="39" customHeight="1">
       <c r="B19" s="9"/>
       <c r="C19" s="14">
         <v>0.66666666666666663</v>
       </c>
-      <c r="D19" s="28" t="s">
+      <c r="D19" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="E19" s="29"/>
-      <c r="F19" s="30"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="32"/>
     </row>
     <row r="20" spans="2:6" ht="37.950000000000003" customHeight="1">
       <c r="B20" s="3"/>
       <c r="C20" s="19">
         <v>0.6875</v>
       </c>
-      <c r="D20" s="48" t="s">
+      <c r="D20" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="E20" s="49"/>
-      <c r="F20" s="50"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="E16:F18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="D11:F11"/>
     <mergeCell ref="D8:F9"/>
     <mergeCell ref="D15:F15"/>
     <mergeCell ref="D13:D14"/>
@@ -2443,12 +2478,6 @@
     <mergeCell ref="D7:G7"/>
     <mergeCell ref="E13:E14"/>
     <mergeCell ref="F13:F14"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="E16:F18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="D11:F11"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup scale="70" orientation="portrait"/>
@@ -2474,14 +2503,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="13.95" customHeight="1">
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="24"/>
+      <c r="D1" s="48"/>
     </row>
     <row r="2" spans="2:7" ht="43.2" customHeight="1">
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
       <c r="F2" s="2" t="s">
         <v>12</v>
       </c>
@@ -2506,52 +2535,52 @@
       <c r="C4" s="8">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
     </row>
     <row r="5" spans="2:7" ht="46.2" customHeight="1">
       <c r="B5" s="9"/>
       <c r="C5" s="8">
         <v>0.42708333333333331</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="29"/>
-      <c r="F5" s="30"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="32"/>
     </row>
     <row r="6" spans="2:7" ht="43.5" customHeight="1">
       <c r="B6" s="9"/>
       <c r="C6" s="8">
         <v>0.4375</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="29"/>
-      <c r="F6" s="30"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="32"/>
     </row>
     <row r="7" spans="2:7" ht="35.25" customHeight="1" thickBot="1">
       <c r="B7" s="10"/>
       <c r="C7" s="11">
         <v>0.46875</v>
       </c>
-      <c r="D7" s="62" t="s">
+      <c r="D7" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
     </row>
     <row r="8" spans="2:7" ht="60" customHeight="1">
       <c r="B8" s="12"/>
       <c r="C8" s="8">
         <v>0.48958333333333331</v>
       </c>
-      <c r="D8" s="42" t="s">
+      <c r="D8" s="24" t="s">
         <v>15</v>
       </c>
       <c r="E8" s="18" t="s">
@@ -2564,11 +2593,11 @@
     <row r="9" spans="2:7" ht="60" customHeight="1">
       <c r="B9" s="9"/>
       <c r="C9" s="8"/>
-      <c r="D9" s="54"/>
+      <c r="D9" s="63"/>
       <c r="E9" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="65" t="s">
+      <c r="F9" s="60" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2577,49 +2606,49 @@
       <c r="C10" s="8"/>
       <c r="D10" s="16"/>
       <c r="E10" s="67"/>
-      <c r="F10" s="65"/>
+      <c r="F10" s="60"/>
     </row>
     <row r="11" spans="2:7" ht="55.2" customHeight="1">
       <c r="B11" s="10"/>
       <c r="C11" s="11">
         <v>0.54166666666666663</v>
       </c>
-      <c r="D11" s="55" t="s">
+      <c r="D11" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="56"/>
-      <c r="F11" s="56"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="65"/>
     </row>
     <row r="12" spans="2:7" ht="40.950000000000003" customHeight="1">
       <c r="B12" s="9"/>
       <c r="C12" s="8">
         <v>0.57291666666666663</v>
       </c>
-      <c r="D12" s="28" t="s">
+      <c r="D12" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="29"/>
-      <c r="F12" s="30"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="32"/>
     </row>
     <row r="13" spans="2:7" ht="37.950000000000003" customHeight="1">
       <c r="B13" s="9"/>
       <c r="C13" s="8">
         <v>44839.59375</v>
       </c>
-      <c r="D13" s="57"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="59"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="54"/>
     </row>
     <row r="14" spans="2:7" ht="43.2" customHeight="1" thickBot="1">
       <c r="B14" s="13"/>
       <c r="C14" s="11">
         <v>44839.614583333336</v>
       </c>
-      <c r="D14" s="55" t="s">
+      <c r="D14" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="56"/>
-      <c r="F14" s="56"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="65"/>
     </row>
     <row r="15" spans="2:7" ht="88.95" customHeight="1" thickBot="1">
       <c r="B15" s="9"/>
@@ -2629,58 +2658,53 @@
       <c r="D15" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="44" t="s">
+      <c r="E15" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="F15" s="45"/>
+      <c r="F15" s="27"/>
     </row>
     <row r="16" spans="2:7" ht="25.2" customHeight="1">
       <c r="B16" s="9"/>
       <c r="C16" s="14">
         <v>0.65625</v>
       </c>
-      <c r="D16" s="60" t="s">
+      <c r="D16" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="52"/>
-      <c r="F16" s="53"/>
+      <c r="E16" s="61"/>
+      <c r="F16" s="62"/>
     </row>
     <row r="17" spans="2:6" ht="55.2" customHeight="1">
       <c r="B17" s="9"/>
       <c r="C17" s="14"/>
-      <c r="D17" s="61"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="47"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="29"/>
     </row>
     <row r="18" spans="2:6" ht="39" customHeight="1">
       <c r="B18" s="9"/>
       <c r="C18" s="14">
         <v>0.67708333333333337</v>
       </c>
-      <c r="D18" s="28" t="s">
+      <c r="D18" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="29"/>
-      <c r="F18" s="30"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="32"/>
     </row>
     <row r="19" spans="2:6" ht="37.950000000000003" customHeight="1">
       <c r="B19" s="3"/>
       <c r="C19" s="19">
         <v>0.6875</v>
       </c>
-      <c r="D19" s="48" t="s">
+      <c r="D19" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="E19" s="49"/>
-      <c r="F19" s="50"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D12:F13"/>
-    <mergeCell ref="D16:D17"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="D18:F18"/>
     <mergeCell ref="C1:D2"/>
@@ -2691,6 +2715,11 @@
     <mergeCell ref="D6:F6"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E15:F17"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D12:F13"/>
+    <mergeCell ref="D16:D17"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup scale="70" orientation="portrait"/>

--- a/unit-0/paneltalk-agenda/agenda.xlsx
+++ b/unit-0/paneltalk-agenda/agenda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\CertCompScience\2026\workshop1Sept\unit-0\paneltalk-agenda\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{066867AE-5E84-4B17-A010-C56D25676B0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0AFA83E-3A25-4559-B2DA-67E906A8A0F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="41">
   <si>
     <t>Time</t>
   </si>
@@ -192,19 +192,7 @@
 Siobhan Roche &amp; Dr. Frank Walsh</t>
   </si>
   <si>
-    <t xml:space="preserve">Getting to know the Tutors Stack
-(G17)
-Colm Dunphy &amp; Pete Windle
-</t>
-  </si>
-  <si>
     <t>Getting Help and Staying Connected with Slack - Colm Dunphy (F02)</t>
-  </si>
-  <si>
-    <t>Getting Help and Staying Connected with Slack - Colm Dunphy (E19B)</t>
-  </si>
-  <si>
-    <t>Online Learning Experience - Laura Mc Gibney (E19B)</t>
   </si>
   <si>
     <t>The Evolution of Machine Learning and AI - Indrakshi Dey  (F02)</t>
@@ -236,9 +224,6 @@
     </r>
   </si>
   <si>
-    <t>Online Learning Experience - Laura McGibney (F02)</t>
-  </si>
-  <si>
     <t>Data Handling and Infrastructure for AI - Tamas Grotz, Abdul Wahid.</t>
   </si>
   <si>
@@ -264,6 +249,18 @@
     <t>Python Programming WorkShop 
  - Bring your laptop and get help with software installation  (IT118)
 Siobhan Roche &amp; Mairead Meagher</t>
+  </si>
+  <si>
+    <t>Online Learning Experience - Laura Mc Gibney (F02)</t>
+  </si>
+  <si>
+    <t>Cert AI &amp; ML</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Getting to know the Tutors 
+(G17)
+Colm Dunphy &amp; Pete Windle
+</t>
   </si>
 </sst>
 </file>
@@ -702,23 +699,17 @@
     <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -727,18 +718,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -774,17 +753,50 @@
     <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -812,21 +824,6 @@
     </xf>
     <xf numFmtId="49" fontId="5" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1987,14 +1984,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" ht="13.95" customHeight="1">
-      <c r="C1" s="48" t="s">
+      <c r="C1" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="48"/>
+      <c r="D1" s="24"/>
     </row>
     <row r="2" spans="2:14" ht="43.2" customHeight="1">
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
       <c r="F2" s="2" t="s">
         <v>12</v>
       </c>
@@ -2011,7 +2008,7 @@
         <v>10</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="2:14" ht="30" customHeight="1">
@@ -2019,50 +2016,50 @@
       <c r="C4" s="8">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D4" s="50" t="s">
+      <c r="D4" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
     </row>
     <row r="5" spans="2:14" ht="64.2" customHeight="1">
       <c r="B5" s="9"/>
       <c r="C5" s="8">
         <v>0.42708333333333331</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="31"/>
-      <c r="F5" s="32"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="30"/>
     </row>
     <row r="6" spans="2:14" ht="64.8" customHeight="1">
       <c r="B6" s="9"/>
       <c r="C6" s="8">
         <v>0.4375</v>
       </c>
-      <c r="D6" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="31"/>
-      <c r="F6" s="32"/>
-      <c r="K6" s="30" t="s">
+      <c r="D6" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="29"/>
+      <c r="F6" s="30"/>
+      <c r="K6" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="L6" s="31"/>
-      <c r="M6" s="32"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="30"/>
     </row>
     <row r="7" spans="2:14" ht="35.25" customHeight="1">
       <c r="B7" s="10"/>
       <c r="C7" s="11">
         <v>0.46875</v>
       </c>
-      <c r="D7" s="37" t="s">
+      <c r="D7" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="39"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="33"/>
     </row>
     <row r="8" spans="2:14" ht="44.25" customHeight="1">
       <c r="B8" s="12"/>
@@ -2070,24 +2067,22 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" s="23" t="s">
-        <v>29</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="E8" s="44" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="45"/>
     </row>
     <row r="9" spans="2:14" ht="18">
       <c r="B9" s="9"/>
       <c r="C9" s="15">
         <v>0.51041666666666663</v>
       </c>
-      <c r="D9" s="37"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="39"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="33"/>
     </row>
     <row r="10" spans="2:14" ht="37.5" customHeight="1">
       <c r="B10" s="9"/>
@@ -2097,42 +2092,40 @@
       <c r="D10" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="L10" s="40" t="s">
+      <c r="E10" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="45"/>
+      <c r="L10" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="M10" s="41"/>
-      <c r="N10" s="41"/>
+      <c r="M10" s="35"/>
+      <c r="N10" s="35"/>
     </row>
     <row r="11" spans="2:14" ht="55.2" customHeight="1">
       <c r="B11" s="10"/>
       <c r="C11" s="11">
         <v>0.54166666666666663</v>
       </c>
-      <c r="D11" s="42" t="s">
+      <c r="D11" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="37"/>
     </row>
     <row r="12" spans="2:14" ht="66" customHeight="1">
       <c r="B12" s="9"/>
       <c r="C12" s="15">
         <v>0.57291666666666663</v>
       </c>
-      <c r="D12" s="36" t="s">
-        <v>40</v>
+      <c r="D12" s="51" t="s">
+        <v>36</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F12" s="23" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>25</v>
@@ -2143,85 +2136,78 @@
       <c r="C13" s="15">
         <v>44839.59375</v>
       </c>
-      <c r="D13" s="36"/>
-      <c r="E13" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="F13" s="45" t="s">
-        <v>35</v>
+      <c r="D13" s="51"/>
+      <c r="E13" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="39" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="2:14" ht="24" hidden="1" customHeight="1">
       <c r="B14" s="9"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="45"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="39"/>
     </row>
     <row r="15" spans="2:14" ht="43.2" customHeight="1">
       <c r="B15" s="13"/>
       <c r="C15" s="11">
         <v>44839.614583333336</v>
       </c>
-      <c r="D15" s="46" t="s">
+      <c r="D15" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
     </row>
     <row r="16" spans="2:14" ht="88.95" customHeight="1">
       <c r="B16" s="9"/>
       <c r="C16" s="15">
         <v>44839.635416666664</v>
       </c>
-      <c r="D16" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="E16" s="26" t="s">
+      <c r="D16" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="F16" s="27"/>
+      <c r="E16" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="45"/>
+      <c r="M16" s="23" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="17" spans="2:6" ht="1.8" customHeight="1">
       <c r="B17" s="9"/>
       <c r="C17" s="14"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="29"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="47"/>
     </row>
     <row r="18" spans="2:6" ht="60" customHeight="1">
       <c r="B18" s="9"/>
       <c r="C18" s="14">
         <v>0.66666666666666663</v>
       </c>
-      <c r="D18" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="E18" s="31"/>
-      <c r="F18" s="32"/>
+      <c r="D18" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="29"/>
+      <c r="F18" s="30"/>
     </row>
     <row r="19" spans="2:6" ht="37.950000000000003" customHeight="1">
       <c r="B19" s="3"/>
       <c r="C19" s="19">
         <v>0.6875</v>
       </c>
-      <c r="D19" s="33" t="s">
+      <c r="D19" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="E19" s="34"/>
-      <c r="F19" s="35"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="50"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="C1:D2"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="D7:G7"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="D15:F15"/>
+  <mergeCells count="19">
     <mergeCell ref="D16:D17"/>
     <mergeCell ref="E16:F17"/>
     <mergeCell ref="D18:F18"/>
@@ -2229,6 +2215,18 @@
     <mergeCell ref="D6:F6"/>
     <mergeCell ref="D12:D14"/>
     <mergeCell ref="D9:G9"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="C1:D2"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="D7:G7"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup scale="70" orientation="portrait"/>
@@ -2254,14 +2252,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="13.95" customHeight="1">
-      <c r="C1" s="48" t="s">
+      <c r="C1" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="48"/>
+      <c r="D1" s="24"/>
     </row>
     <row r="2" spans="2:7" ht="43.2" customHeight="1">
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
       <c r="F2" s="2" t="s">
         <v>12</v>
       </c>
@@ -2286,83 +2284,83 @@
       <c r="C4" s="8">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D4" s="50" t="s">
+      <c r="D4" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
     </row>
     <row r="5" spans="2:7" ht="46.2" customHeight="1">
       <c r="B5" s="9"/>
       <c r="C5" s="8">
         <v>0.42708333333333331</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="31"/>
-      <c r="F5" s="32"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="30"/>
     </row>
     <row r="6" spans="2:7" ht="43.5" customHeight="1">
       <c r="B6" s="9"/>
       <c r="C6" s="8">
         <v>0.4375</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="31"/>
-      <c r="F6" s="32"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="30"/>
     </row>
     <row r="7" spans="2:7" ht="35.25" customHeight="1">
       <c r="B7" s="10"/>
       <c r="C7" s="11">
         <v>0.46875</v>
       </c>
-      <c r="D7" s="57" t="s">
+      <c r="D7" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
     </row>
     <row r="8" spans="2:7" ht="44.25" customHeight="1">
       <c r="B8" s="12"/>
       <c r="C8" s="8">
         <v>0.48958333333333331</v>
       </c>
-      <c r="D8" s="30" t="s">
+      <c r="D8" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="30"/>
     </row>
     <row r="9" spans="2:7" ht="29.25" customHeight="1">
       <c r="B9" s="9"/>
       <c r="C9" s="8"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="54"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="59"/>
     </row>
     <row r="10" spans="2:7" ht="37.5" customHeight="1">
       <c r="B10" s="9"/>
       <c r="C10" s="8"/>
-      <c r="D10" s="40" t="s">
+      <c r="D10" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
     </row>
     <row r="11" spans="2:7" ht="55.2" customHeight="1" thickBot="1">
       <c r="B11" s="10"/>
       <c r="C11" s="11">
         <v>0.54166666666666663</v>
       </c>
-      <c r="D11" s="64" t="s">
+      <c r="D11" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="65"/>
-      <c r="F11" s="65"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="56"/>
     </row>
     <row r="12" spans="2:7" ht="40.950000000000003" customHeight="1" thickBot="1">
       <c r="B12" s="9"/>
@@ -2384,90 +2382,84 @@
       <c r="C13" s="8">
         <v>44839.59375</v>
       </c>
-      <c r="D13" s="55" t="s">
+      <c r="D13" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="58" t="s">
+      <c r="E13" s="63" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="60" t="s">
+      <c r="F13" s="65" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="24" hidden="1" customHeight="1">
       <c r="B14" s="9"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="59"/>
-      <c r="F14" s="60"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="65"/>
     </row>
     <row r="15" spans="2:7" ht="43.2" customHeight="1">
       <c r="B15" s="13"/>
       <c r="C15" s="11">
         <v>44839.614583333336</v>
       </c>
-      <c r="D15" s="46" t="s">
+      <c r="D15" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
     </row>
     <row r="16" spans="2:7" ht="88.95" customHeight="1">
       <c r="B16" s="9"/>
       <c r="C16" s="15">
         <v>44839.635416666664</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="26" t="s">
+      <c r="E16" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="F16" s="27"/>
+      <c r="F16" s="45"/>
     </row>
     <row r="17" spans="2:6" ht="25.2" customHeight="1">
       <c r="B17" s="9"/>
       <c r="C17" s="14"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="61"/>
-      <c r="F17" s="62"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="53"/>
     </row>
     <row r="18" spans="2:6" ht="55.2" customHeight="1">
       <c r="B18" s="9"/>
       <c r="C18" s="14"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="29"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="47"/>
     </row>
     <row r="19" spans="2:6" ht="39" customHeight="1">
       <c r="B19" s="9"/>
       <c r="C19" s="14">
         <v>0.66666666666666663</v>
       </c>
-      <c r="D19" s="30" t="s">
+      <c r="D19" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="E19" s="31"/>
-      <c r="F19" s="32"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="30"/>
     </row>
     <row r="20" spans="2:6" ht="37.950000000000003" customHeight="1">
       <c r="B20" s="3"/>
       <c r="C20" s="19">
         <v>0.6875</v>
       </c>
-      <c r="D20" s="33" t="s">
+      <c r="D20" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="E20" s="34"/>
-      <c r="F20" s="35"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="E16:F18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="D11:F11"/>
     <mergeCell ref="D8:F9"/>
     <mergeCell ref="D15:F15"/>
     <mergeCell ref="D13:D14"/>
@@ -2478,6 +2470,12 @@
     <mergeCell ref="D7:G7"/>
     <mergeCell ref="E13:E14"/>
     <mergeCell ref="F13:F14"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="E16:F18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="D11:F11"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup scale="70" orientation="portrait"/>
@@ -2503,14 +2501,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="13.95" customHeight="1">
-      <c r="C1" s="48" t="s">
+      <c r="C1" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="48"/>
+      <c r="D1" s="24"/>
     </row>
     <row r="2" spans="2:7" ht="43.2" customHeight="1">
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
       <c r="F2" s="2" t="s">
         <v>12</v>
       </c>
@@ -2535,52 +2533,52 @@
       <c r="C4" s="8">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D4" s="50" t="s">
+      <c r="D4" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
     </row>
     <row r="5" spans="2:7" ht="46.2" customHeight="1">
       <c r="B5" s="9"/>
       <c r="C5" s="8">
         <v>0.42708333333333331</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="31"/>
-      <c r="F5" s="32"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="30"/>
     </row>
     <row r="6" spans="2:7" ht="43.5" customHeight="1">
       <c r="B6" s="9"/>
       <c r="C6" s="8">
         <v>0.4375</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="31"/>
-      <c r="F6" s="32"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="30"/>
     </row>
     <row r="7" spans="2:7" ht="35.25" customHeight="1" thickBot="1">
       <c r="B7" s="10"/>
       <c r="C7" s="11">
         <v>0.46875</v>
       </c>
-      <c r="D7" s="57" t="s">
+      <c r="D7" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
     </row>
     <row r="8" spans="2:7" ht="60" customHeight="1">
       <c r="B8" s="12"/>
       <c r="C8" s="8">
         <v>0.48958333333333331</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="42" t="s">
         <v>15</v>
       </c>
       <c r="E8" s="18" t="s">
@@ -2593,11 +2591,11 @@
     <row r="9" spans="2:7" ht="60" customHeight="1">
       <c r="B9" s="9"/>
       <c r="C9" s="8"/>
-      <c r="D9" s="63"/>
+      <c r="D9" s="54"/>
       <c r="E9" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="60" t="s">
+      <c r="F9" s="65" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2606,49 +2604,49 @@
       <c r="C10" s="8"/>
       <c r="D10" s="16"/>
       <c r="E10" s="67"/>
-      <c r="F10" s="60"/>
+      <c r="F10" s="65"/>
     </row>
     <row r="11" spans="2:7" ht="55.2" customHeight="1">
       <c r="B11" s="10"/>
       <c r="C11" s="11">
         <v>0.54166666666666663</v>
       </c>
-      <c r="D11" s="64" t="s">
+      <c r="D11" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="65"/>
-      <c r="F11" s="65"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="56"/>
     </row>
     <row r="12" spans="2:7" ht="40.950000000000003" customHeight="1">
       <c r="B12" s="9"/>
       <c r="C12" s="8">
         <v>0.57291666666666663</v>
       </c>
-      <c r="D12" s="30" t="s">
+      <c r="D12" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="31"/>
-      <c r="F12" s="32"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="30"/>
     </row>
     <row r="13" spans="2:7" ht="37.950000000000003" customHeight="1">
       <c r="B13" s="9"/>
       <c r="C13" s="8">
         <v>44839.59375</v>
       </c>
-      <c r="D13" s="52"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="54"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="58"/>
+      <c r="F13" s="59"/>
     </row>
     <row r="14" spans="2:7" ht="43.2" customHeight="1" thickBot="1">
       <c r="B14" s="13"/>
       <c r="C14" s="11">
         <v>44839.614583333336</v>
       </c>
-      <c r="D14" s="64" t="s">
+      <c r="D14" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="65"/>
-      <c r="F14" s="65"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="56"/>
     </row>
     <row r="15" spans="2:7" ht="88.95" customHeight="1" thickBot="1">
       <c r="B15" s="9"/>
@@ -2658,53 +2656,58 @@
       <c r="D15" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="26" t="s">
+      <c r="E15" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="F15" s="27"/>
+      <c r="F15" s="45"/>
     </row>
     <row r="16" spans="2:7" ht="25.2" customHeight="1">
       <c r="B16" s="9"/>
       <c r="C16" s="14">
         <v>0.65625</v>
       </c>
-      <c r="D16" s="55" t="s">
+      <c r="D16" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="61"/>
-      <c r="F16" s="62"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="53"/>
     </row>
     <row r="17" spans="2:6" ht="55.2" customHeight="1">
       <c r="B17" s="9"/>
       <c r="C17" s="14"/>
-      <c r="D17" s="56"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="29"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="47"/>
     </row>
     <row r="18" spans="2:6" ht="39" customHeight="1">
       <c r="B18" s="9"/>
       <c r="C18" s="14">
         <v>0.67708333333333337</v>
       </c>
-      <c r="D18" s="30" t="s">
+      <c r="D18" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="31"/>
-      <c r="F18" s="32"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="30"/>
     </row>
     <row r="19" spans="2:6" ht="37.950000000000003" customHeight="1">
       <c r="B19" s="3"/>
       <c r="C19" s="19">
         <v>0.6875</v>
       </c>
-      <c r="D19" s="33" t="s">
+      <c r="D19" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="E19" s="34"/>
-      <c r="F19" s="35"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D12:F13"/>
+    <mergeCell ref="D16:D17"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="D18:F18"/>
     <mergeCell ref="C1:D2"/>
@@ -2715,11 +2718,6 @@
     <mergeCell ref="D6:F6"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E15:F17"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D12:F13"/>
-    <mergeCell ref="D16:D17"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup scale="70" orientation="portrait"/>
